--- a/diseases/d100/2026-2029.xlsx
+++ b/diseases/d100/2026-2029.xlsx
@@ -43503,12 +43503,12 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -43542,81 +43542,100 @@
         </is>
       </c>
       <c r="N248" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="O248" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="R248" t="n">
-        <v>0.009454625838138971</v>
+        <v>0.2242771302788003</v>
       </c>
       <c r="S248" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U248" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HAEMOPHILUS_INVASIVE</t>
+        </is>
+      </c>
+      <c r="AA248" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO248" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP248" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ248" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR248" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS248" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS248" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HAEMOPHILUS_INVASIVE</t>
+        </is>
+      </c>
       <c r="AT248" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU248" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV248" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ248" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA248" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB248" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC248" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -43643,17 +43662,17 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -43678,7 +43697,7 @@
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M249" t="inlineStr">
@@ -43687,81 +43706,175 @@
         </is>
       </c>
       <c r="N249" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="O249" t="n">
-        <v>6</v>
-      </c>
-      <c r="R249" t="n">
-        <v>0.004900850445394598</v>
-      </c>
-      <c r="S249" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>24</v>
+      </c>
+      <c r="U249" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HAEMOPHILUS_INVASIVE</t>
+        </is>
+      </c>
+      <c r="V249" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HAEMOPHILUS_INVASIVE</t>
+        </is>
+      </c>
+      <c r="W249" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X249" t="inlineStr">
+        <is>
+          <t>Invasiv infektion med Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="Y249" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z249" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA249" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB249" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC249" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD249" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE249" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF249" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG249" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH249" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI249" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ249" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK249" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; Source is invasive disease and is not assumed to be type b only.</t>
+        </is>
+      </c>
+      <c r="AM249" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN249" t="b">
+        <v>1</v>
       </c>
       <c r="AO249" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP249" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ249" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR249" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS249" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS249" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HAEMOPHILUS_INVASIVE</t>
+        </is>
+      </c>
       <c r="AT249" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU249" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV249" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW249" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ249" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA249" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB249" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC249" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -43793,12 +43906,12 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -43823,7 +43936,7 @@
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
@@ -43832,93 +43945,81 @@
         </is>
       </c>
       <c r="N250" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="O250" t="n">
-        <v>0</v>
-      </c>
-      <c r="P250" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="R250" t="n">
-        <v>0</v>
+        <v>0.009454625838138971</v>
       </c>
       <c r="S250" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA250" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO250" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP250" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ250" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS250" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B; SER_SG_HIST_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR250" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS250" t="inlineStr"/>
       <c r="AT250" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU250" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV250" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ250" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA250" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB250" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC250" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -43945,17 +44046,17 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -43989,173 +44090,81 @@
         </is>
       </c>
       <c r="N251" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O251" t="n">
-        <v>0</v>
-      </c>
-      <c r="P251" t="n">
-        <v>0</v>
-      </c>
-      <c r="U251" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
-      <c r="V251" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
-      <c r="W251" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X251" t="inlineStr">
-        <is>
-          <t>Haemophilus influenzae type b</t>
-        </is>
-      </c>
-      <c r="Y251" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z251" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA251" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB251" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC251" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD251" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE251" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF251" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG251" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH251" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI251" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ251" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK251" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM251" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN251" t="b">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="R251" t="n">
+        <v>0.004900850445394598</v>
+      </c>
+      <c r="S251" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO251" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP251" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ251" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS251" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B; SER_SG_HIST_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR251" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS251" t="inlineStr"/>
       <c r="AT251" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU251" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV251" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW251" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ251" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA251" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB251" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC251" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -44187,12 +44196,12 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -44217,7 +44226,7 @@
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M252" t="inlineStr">
@@ -44226,81 +44235,93 @@
         </is>
       </c>
       <c r="N252" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="O252" t="n">
-        <v>41</v>
+        <v>0</v>
+      </c>
+      <c r="P252" t="n">
+        <v>0</v>
       </c>
       <c r="R252" t="n">
-        <v>0.01174665634435448</v>
+        <v>0</v>
       </c>
       <c r="S252" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA252" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO252" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP252" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR252" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS252" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ252" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS252" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B; SER_SG_HIST_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
       <c r="AT252" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU252" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV252" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW252" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ252" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA252" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB252" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC252" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -44327,17 +44348,17 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -44362,7 +44383,7 @@
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M253" t="inlineStr">
@@ -44371,81 +44392,173 @@
         </is>
       </c>
       <c r="N253" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O253" t="n">
-        <v>6</v>
-      </c>
-      <c r="R253" t="n">
-        <v>0.004900850445394598</v>
-      </c>
-      <c r="S253" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="P253" t="n">
+        <v>0</v>
+      </c>
+      <c r="U253" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
+      <c r="V253" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
+      <c r="W253" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X253" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae type b</t>
+        </is>
+      </c>
+      <c r="Y253" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z253" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA253" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB253" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC253" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD253" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE253" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF253" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG253" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH253" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI253" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ253" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK253" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM253" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN253" t="b">
+        <v>1</v>
       </c>
       <c r="AO253" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP253" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR253" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS253" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ253" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS253" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B; SER_SG_HIST_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
       <c r="AT253" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU253" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV253" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ253" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA253" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB253" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC253" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -44477,12 +44590,12 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -44507,7 +44620,7 @@
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M254" t="inlineStr">
@@ -44516,93 +44629,81 @@
         </is>
       </c>
       <c r="N254" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="O254" t="n">
-        <v>0</v>
-      </c>
-      <c r="P254" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="R254" t="n">
-        <v>0</v>
+        <v>0.01174665634435448</v>
       </c>
       <c r="S254" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA254" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO254" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP254" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ254" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS254" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B; SER_SG_HIST_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR254" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS254" t="inlineStr"/>
       <c r="AT254" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU254" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV254" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW254" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ254" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA254" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB254" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC254" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -44629,17 +44730,17 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -44673,173 +44774,81 @@
         </is>
       </c>
       <c r="N255" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O255" t="n">
-        <v>0</v>
-      </c>
-      <c r="P255" t="n">
-        <v>0</v>
-      </c>
-      <c r="U255" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
-      <c r="V255" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
-      <c r="W255" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X255" t="inlineStr">
-        <is>
-          <t>Haemophilus influenzae type b</t>
-        </is>
-      </c>
-      <c r="Y255" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z255" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA255" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB255" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC255" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD255" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE255" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF255" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG255" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH255" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI255" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ255" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK255" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM255" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN255" t="b">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="R255" t="n">
+        <v>0.004900850445394598</v>
+      </c>
+      <c r="S255" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO255" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP255" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ255" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS255" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B; SER_SG_HIST_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR255" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS255" t="inlineStr"/>
       <c r="AT255" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU255" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV255" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW255" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX255" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY255" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ255" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA255" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB255" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC255" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -44871,12 +44880,12 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -44901,7 +44910,7 @@
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M256" t="inlineStr">
@@ -44910,81 +44919,93 @@
         </is>
       </c>
       <c r="N256" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="O256" t="n">
-        <v>38</v>
+        <v>0</v>
+      </c>
+      <c r="P256" t="n">
+        <v>0</v>
       </c>
       <c r="R256" t="n">
-        <v>0.01088714490452366</v>
+        <v>0</v>
       </c>
       <c r="S256" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA256" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO256" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP256" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR256" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS256" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ256" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS256" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B; SER_SG_HIST_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
       <c r="AT256" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU256" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV256" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW256" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY256" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ256" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA256" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB256" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC256" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -45011,17 +45032,17 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -45046,7 +45067,7 @@
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M257" t="inlineStr">
@@ -45055,81 +45076,173 @@
         </is>
       </c>
       <c r="N257" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O257" t="n">
-        <v>14</v>
-      </c>
-      <c r="R257" t="n">
-        <v>0.01143531770592073</v>
-      </c>
-      <c r="S257" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="P257" t="n">
+        <v>0</v>
+      </c>
+      <c r="U257" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
+      <c r="V257" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
+      <c r="W257" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X257" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae type b</t>
+        </is>
+      </c>
+      <c r="Y257" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z257" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA257" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB257" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC257" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD257" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE257" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF257" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG257" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH257" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI257" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ257" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK257" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM257" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN257" t="b">
+        <v>1</v>
       </c>
       <c r="AO257" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP257" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR257" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS257" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ257" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS257" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B; SER_SG_HIST_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
       <c r="AT257" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU257" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV257" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW257" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX257" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY257" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ257" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA257" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB257" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC257" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -45161,12 +45274,12 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -45191,7 +45304,7 @@
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M258" t="inlineStr">
@@ -45200,93 +45313,81 @@
         </is>
       </c>
       <c r="N258" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="O258" t="n">
-        <v>0</v>
-      </c>
-      <c r="P258" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="R258" t="n">
-        <v>0</v>
+        <v>0.01088714490452366</v>
       </c>
       <c r="S258" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA258" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO258" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP258" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ258" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS258" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B; SER_SG_HIST_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR258" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS258" t="inlineStr"/>
       <c r="AT258" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU258" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV258" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW258" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX258" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY258" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ258" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA258" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB258" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC258" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -45313,17 +45414,17 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -45357,173 +45458,81 @@
         </is>
       </c>
       <c r="N259" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O259" t="n">
-        <v>0</v>
-      </c>
-      <c r="P259" t="n">
-        <v>0</v>
-      </c>
-      <c r="U259" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
-      <c r="V259" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
-      <c r="W259" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X259" t="inlineStr">
-        <is>
-          <t>Haemophilus influenzae type b</t>
-        </is>
-      </c>
-      <c r="Y259" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z259" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA259" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB259" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC259" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD259" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE259" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF259" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG259" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH259" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI259" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ259" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK259" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM259" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN259" t="b">
-        <v>1</v>
+        <v>14</v>
+      </c>
+      <c r="R259" t="n">
+        <v>0.01143531770592073</v>
+      </c>
+      <c r="S259" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO259" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP259" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ259" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS259" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B; SER_SG_HIST_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR259" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS259" t="inlineStr"/>
       <c r="AT259" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU259" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV259" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW259" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX259" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY259" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ259" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA259" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB259" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC259" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -45555,12 +45564,12 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -45585,7 +45594,7 @@
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M260" t="inlineStr">
@@ -45594,81 +45603,93 @@
         </is>
       </c>
       <c r="N260" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="O260" t="n">
-        <v>30</v>
+        <v>0</v>
+      </c>
+      <c r="P260" t="n">
+        <v>0</v>
       </c>
       <c r="R260" t="n">
-        <v>0.008595114398308155</v>
+        <v>0</v>
       </c>
       <c r="S260" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA260" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO260" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP260" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR260" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS260" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ260" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS260" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B; SER_SG_HIST_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
       <c r="AT260" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU260" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV260" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW260" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY260" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ260" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA260" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB260" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC260" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -45695,17 +45716,17 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -45730,7 +45751,7 @@
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M261" t="inlineStr">
@@ -45739,81 +45760,173 @@
         </is>
       </c>
       <c r="N261" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O261" t="n">
-        <v>8</v>
-      </c>
-      <c r="R261" t="n">
-        <v>0.00653446726052613</v>
-      </c>
-      <c r="S261" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="P261" t="n">
+        <v>0</v>
+      </c>
+      <c r="U261" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
+      <c r="V261" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
+      <c r="W261" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X261" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae type b</t>
+        </is>
+      </c>
+      <c r="Y261" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z261" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA261" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB261" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC261" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD261" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE261" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF261" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG261" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH261" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI261" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ261" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK261" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM261" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN261" t="b">
+        <v>1</v>
       </c>
       <c r="AO261" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP261" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR261" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS261" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ261" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS261" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B; SER_SG_HIST_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
       <c r="AT261" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU261" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV261" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW261" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX261" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY261" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ261" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA261" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB261" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC261" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -45845,12 +45958,12 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -45875,7 +45988,7 @@
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M262" t="inlineStr">
@@ -45884,93 +45997,81 @@
         </is>
       </c>
       <c r="N262" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="O262" t="n">
-        <v>0</v>
-      </c>
-      <c r="P262" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="R262" t="n">
-        <v>0</v>
+        <v>0.008595114398308155</v>
       </c>
       <c r="S262" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA262" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO262" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP262" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ262" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS262" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B; SER_SG_HIST_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR262" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS262" t="inlineStr"/>
       <c r="AT262" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU262" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV262" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW262" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX262" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY262" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ262" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA262" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB262" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC262" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -45997,17 +46098,17 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -46041,173 +46142,81 @@
         </is>
       </c>
       <c r="N263" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O263" t="n">
-        <v>0</v>
-      </c>
-      <c r="P263" t="n">
-        <v>0</v>
-      </c>
-      <c r="U263" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
-      <c r="V263" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
-      <c r="W263" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X263" t="inlineStr">
-        <is>
-          <t>Haemophilus influenzae type b</t>
-        </is>
-      </c>
-      <c r="Y263" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z263" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA263" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB263" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC263" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD263" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE263" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF263" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG263" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH263" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI263" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ263" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK263" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM263" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN263" t="b">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="R263" t="n">
+        <v>0.00653446726052613</v>
+      </c>
+      <c r="S263" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO263" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP263" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ263" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS263" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B; SER_SG_HIST_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR263" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS263" t="inlineStr"/>
       <c r="AT263" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU263" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV263" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW263" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX263" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY263" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ263" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA263" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB263" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC263" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -46239,12 +46248,12 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -46269,7 +46278,7 @@
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M264" t="inlineStr">
@@ -46278,81 +46287,93 @@
         </is>
       </c>
       <c r="N264" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="O264" t="n">
-        <v>36</v>
+        <v>0</v>
+      </c>
+      <c r="P264" t="n">
+        <v>0</v>
       </c>
       <c r="R264" t="n">
-        <v>0.01031413727796979</v>
+        <v>0</v>
       </c>
       <c r="S264" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA264" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO264" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP264" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR264" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS264" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ264" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS264" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B; SER_SG_HIST_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
       <c r="AT264" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU264" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV264" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW264" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX264" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY264" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ264" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA264" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB264" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC264" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -46379,17 +46400,17 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -46414,12 +46435,12 @@
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N265" t="n">
@@ -46428,76 +46449,168 @@
       <c r="O265" t="n">
         <v>0</v>
       </c>
-      <c r="R265" t="n">
-        <v>0</v>
-      </c>
-      <c r="S265" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P265" t="n">
+        <v>0</v>
+      </c>
+      <c r="U265" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
+      <c r="V265" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
+      <c r="W265" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X265" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae type b</t>
+        </is>
+      </c>
+      <c r="Y265" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z265" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA265" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB265" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC265" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD265" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE265" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF265" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG265" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH265" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI265" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ265" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK265" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM265" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN265" t="b">
+        <v>1</v>
       </c>
       <c r="AO265" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP265" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR265" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS265" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ265" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS265" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B; SER_SG_HIST_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
       <c r="AT265" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU265" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV265" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW265" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX265" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY265" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ265" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA265" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB265" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC265" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -46529,12 +46642,12 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -46559,109 +46672,90 @@
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N266" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="O266" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="R266" t="n">
-        <v>0</v>
+        <v>0.01031413727796979</v>
       </c>
       <c r="S266" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U266" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1459</t>
-        </is>
-      </c>
-      <c r="AA266" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO266" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP266" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ266" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR266" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS266" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1459</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS266" t="inlineStr"/>
       <c r="AT266" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU266" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV266" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW266" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX266" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY266" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ266" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA266" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB266" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC266" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -46688,17 +46782,17 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -46737,170 +46831,76 @@
       <c r="O267" t="n">
         <v>0</v>
       </c>
-      <c r="U267" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1459</t>
-        </is>
-      </c>
-      <c r="V267" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1459</t>
-        </is>
-      </c>
-      <c r="W267" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X267" t="inlineStr">
-        <is>
-          <t>Haemophilus influenzae,total</t>
-        </is>
-      </c>
-      <c r="Y267" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z267" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA267" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB267" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC267" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD267" t="inlineStr">
+      <c r="R267" t="n">
+        <v>0</v>
+      </c>
+      <c r="S267" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO267" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP267" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR267" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS267" t="inlineStr"/>
+      <c r="AT267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU267" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV267" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE267" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF267" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG267" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH267" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI267" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ267" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK267" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Use the THL reported total; serotype child rows remain independent unprojected series.</t>
-        </is>
-      </c>
-      <c r="AM267" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN267" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO267" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP267" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ267" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR267" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS267" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1459</t>
-        </is>
-      </c>
-      <c r="AT267" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU267" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV267" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW267" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX267" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY267" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ267" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA267" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB267" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC267" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -46932,12 +46932,12 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -46984,68 +46984,87 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U268" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1459</t>
+        </is>
+      </c>
+      <c r="AA268" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO268" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP268" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ268" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR268" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS268" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS268" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1459</t>
+        </is>
+      </c>
       <c r="AT268" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU268" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV268" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW268" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX268" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY268" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ268" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA268" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB268" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC268" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -47072,17 +47091,17 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -47121,17 +47140,34 @@
       <c r="O269" t="n">
         <v>0</v>
       </c>
-      <c r="R269" t="n">
-        <v>0</v>
-      </c>
-      <c r="S269" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U269" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1459</t>
+        </is>
+      </c>
+      <c r="V269" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1459</t>
+        </is>
+      </c>
+      <c r="W269" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X269" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae,total</t>
+        </is>
+      </c>
+      <c r="Y269" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z269" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA269" t="inlineStr">
@@ -47139,6 +47175,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB269" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC269" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD269" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE269" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF269" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG269" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH269" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI269" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ269" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK269" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Use the THL reported total; serotype child rows remain independent unprojected series.</t>
+        </is>
+      </c>
+      <c r="AM269" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN269" t="b">
+        <v>1</v>
+      </c>
       <c r="AO269" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -47151,7 +47245,7 @@
       </c>
       <c r="AQ269" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR269" t="inlineStr">
@@ -47161,7 +47255,7 @@
       </c>
       <c r="AS269" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="AT269" t="n">
@@ -47169,47 +47263,47 @@
       </c>
       <c r="AU269" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV269" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW269" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX269" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY269" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ269" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA269" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB269" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC269" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -47236,217 +47330,526 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>流感嗜血杆菌</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N270" t="n">
+        <v>0</v>
+      </c>
+      <c r="O270" t="n">
+        <v>0</v>
+      </c>
+      <c r="R270" t="n">
+        <v>0</v>
+      </c>
+      <c r="S270" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO270" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP270" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR270" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS270" t="inlineStr"/>
+      <c r="AT270" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU270" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV270" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW270" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX270" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY270" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ270" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA270" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB270" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC270" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>haemophilus-influenzae</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>流感嗜血杆菌</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N271" t="n">
+        <v>0</v>
+      </c>
+      <c r="O271" t="n">
+        <v>0</v>
+      </c>
+      <c r="R271" t="n">
+        <v>0</v>
+      </c>
+      <c r="S271" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U271" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_103_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA271" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO271" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP271" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ271" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR271" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS271" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_103_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT271" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU271" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV271" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW271" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX271" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY271" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ271" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA271" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB271" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC271" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>haemophilus-influenzae</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
           <t>source_series_observation</t>
         </is>
       </c>
-      <c r="F270" t="inlineStr">
+      <c r="F272" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G270" t="inlineStr">
+      <c r="G272" t="inlineStr">
         <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="H270" t="inlineStr">
-        <is>
-          <t>D100</t>
-        </is>
-      </c>
-      <c r="I270" t="inlineStr">
-        <is>
-          <t>Haemophilus influenzae</t>
-        </is>
-      </c>
-      <c r="J270" t="inlineStr">
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
         <is>
           <t>流感嗜血杆菌</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr">
+      <c r="K272" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L270" t="inlineStr">
+      <c r="L272" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="M270" t="inlineStr">
+      <c r="M272" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N270" t="n">
-        <v>0</v>
-      </c>
-      <c r="O270" t="n">
-        <v>0</v>
-      </c>
-      <c r="U270" t="inlineStr">
+      <c r="N272" t="n">
+        <v>0</v>
+      </c>
+      <c r="O272" t="n">
+        <v>0</v>
+      </c>
+      <c r="U272" t="inlineStr">
         <is>
           <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
-      <c r="V270" t="inlineStr">
+      <c r="V272" t="inlineStr">
         <is>
           <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
-      <c r="W270" t="inlineStr">
+      <c r="W272" t="inlineStr">
         <is>
           <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
-      <c r="X270" t="inlineStr">
+      <c r="X272" t="inlineStr">
         <is>
           <t>Syst. H. influenzae-sykdom</t>
         </is>
       </c>
-      <c r="Y270" t="inlineStr">
+      <c r="Y272" t="inlineStr">
         <is>
           <t>case_notifications</t>
         </is>
       </c>
-      <c r="Z270" t="inlineStr">
+      <c r="Z272" t="inlineStr">
         <is>
           <t>national_notifiable_disease_registry</t>
         </is>
       </c>
-      <c r="AA270" t="inlineStr">
+      <c r="AA272" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB270" t="inlineStr">
+      <c r="AB272" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="AC270" t="inlineStr">
+      <c r="AC272" t="inlineStr">
         <is>
           <t>country:NO:national</t>
         </is>
       </c>
-      <c r="AD270" t="inlineStr">
+      <c r="AD272" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE270" t="inlineStr">
+      <c r="AE272" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="AF270" t="inlineStr">
+      <c r="AF272" t="inlineStr">
         <is>
           <t>conditional</t>
         </is>
       </c>
-      <c r="AG270" t="inlineStr">
+      <c r="AG272" t="inlineStr">
         <is>
           <t>non_additive</t>
         </is>
       </c>
-      <c r="AH270" t="inlineStr">
+      <c r="AH272" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="AI270" t="inlineStr">
+      <c r="AI272" t="inlineStr">
         <is>
           <t>missing_is_unknown</t>
         </is>
       </c>
-      <c r="AJ270" t="inlineStr">
+      <c r="AJ272" t="inlineStr">
         <is>
           <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
-      <c r="AK270" t="inlineStr">
+      <c r="AK272" t="inlineStr">
         <is>
           <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic disease mapping.</t>
         </is>
       </c>
-      <c r="AM270" t="inlineStr">
+      <c r="AM272" t="inlineStr">
         <is>
           <t>provisional; raw; revised</t>
         </is>
       </c>
-      <c r="AN270" t="b">
+      <c r="AN272" t="b">
         <v>1</v>
       </c>
-      <c r="AO270" t="inlineStr">
+      <c r="AO272" t="inlineStr">
         <is>
           <t>series_registry</t>
         </is>
       </c>
-      <c r="AP270" t="inlineStr">
+      <c r="AP272" t="inlineStr">
         <is>
           <t>representative_series</t>
         </is>
       </c>
-      <c r="AQ270" t="inlineStr">
+      <c r="AQ272" t="inlineStr">
         <is>
           <t>parity</t>
         </is>
       </c>
-      <c r="AR270" t="inlineStr">
+      <c r="AR272" t="inlineStr">
         <is>
           <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
-      <c r="AS270" t="inlineStr">
+      <c r="AS272" t="inlineStr">
         <is>
           <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
-      <c r="AT270" t="n">
+      <c r="AT272" t="n">
         <v>2</v>
       </c>
-      <c r="AU270" t="inlineStr">
+      <c r="AU272" t="inlineStr">
         <is>
           <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
-      <c r="AV270" t="inlineStr">
+      <c r="AV272" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW270" t="inlineStr">
+      <c r="AW272" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX270" t="inlineStr">
+      <c r="AX272" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY270" t="inlineStr">
+      <c r="AY272" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ270" t="inlineStr">
+      <c r="AZ272" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA270" t="inlineStr">
+      <c r="BA272" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB270" t="inlineStr">
+      <c r="BB272" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC270" t="inlineStr">
+      <c r="BC272" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -47568,7 +47971,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="10">
@@ -47578,7 +47981,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="11">
@@ -47598,7 +48001,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13">
@@ -47630,7 +48033,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2397</v>
+        <v>2421</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d100/2026-2029.xlsx
+++ b/diseases/d100/2026-2029.xlsx
@@ -46787,12 +46787,12 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -46817,22 +46817,22 @@
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N267" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O267" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R267" t="n">
-        <v>0</v>
+        <v>0.009801700890789196</v>
       </c>
       <c r="S267" t="inlineStr">
         <is>
@@ -46865,42 +46865,42 @@
       </c>
       <c r="AV267" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW267" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX267" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY267" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ267" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA267" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB267" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC267" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -46932,12 +46932,12 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -46984,87 +46984,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U268" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1459</t>
-        </is>
-      </c>
-      <c r="AA268" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO268" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP268" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ268" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR268" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS268" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1459</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS268" t="inlineStr"/>
       <c r="AT268" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU268" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV268" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW268" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX268" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY268" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ268" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA268" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB268" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC268" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -47091,7 +47072,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
@@ -47135,103 +47116,28 @@
         </is>
       </c>
       <c r="N269" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O269" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="R269" t="n">
+        <v>0.01778809170864137</v>
+      </c>
+      <c r="S269" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U269" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
-      <c r="V269" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1459</t>
-        </is>
-      </c>
-      <c r="W269" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X269" t="inlineStr">
-        <is>
-          <t>Haemophilus influenzae,total</t>
-        </is>
-      </c>
-      <c r="Y269" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z269" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA269" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB269" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC269" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD269" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE269" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF269" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG269" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH269" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI269" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ269" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK269" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Use the THL reported total; serotype child rows remain independent unprojected series.</t>
-        </is>
-      </c>
-      <c r="AM269" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN269" t="b">
-        <v>1</v>
       </c>
       <c r="AO269" t="inlineStr">
         <is>
@@ -47330,17 +47236,17 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -47374,81 +47280,175 @@
         </is>
       </c>
       <c r="N270" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O270" t="n">
-        <v>0</v>
-      </c>
-      <c r="R270" t="n">
-        <v>0</v>
-      </c>
-      <c r="S270" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="U270" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1459</t>
+        </is>
+      </c>
+      <c r="V270" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1459</t>
+        </is>
+      </c>
+      <c r="W270" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X270" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae,total</t>
+        </is>
+      </c>
+      <c r="Y270" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z270" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA270" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB270" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC270" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD270" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE270" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF270" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG270" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH270" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI270" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ270" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK270" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Use the THL reported total; serotype child rows remain independent unprojected series.</t>
+        </is>
+      </c>
+      <c r="AM270" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN270" t="b">
+        <v>1</v>
       </c>
       <c r="AO270" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP270" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ270" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR270" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS270" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS270" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1459</t>
+        </is>
+      </c>
       <c r="AT270" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU270" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV270" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW270" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX270" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY270" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ270" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA270" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB270" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC270" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -47480,12 +47480,12 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -47532,87 +47532,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U271" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA271" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO271" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP271" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ271" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR271" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS271" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS271" t="inlineStr"/>
       <c r="AT271" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU271" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV271" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW271" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX271" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY271" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ271" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA271" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB271" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC271" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -47639,7 +47620,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
@@ -47688,98 +47669,23 @@
       <c r="O272" t="n">
         <v>0</v>
       </c>
+      <c r="R272" t="n">
+        <v>0</v>
+      </c>
+      <c r="S272" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U272" t="inlineStr">
         <is>
           <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
-      <c r="V272" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W272" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X272" t="inlineStr">
-        <is>
-          <t>Syst. H. influenzae-sykdom</t>
-        </is>
-      </c>
-      <c r="Y272" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z272" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA272" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB272" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC272" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD272" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE272" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF272" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG272" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH272" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI272" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ272" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK272" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic disease mapping.</t>
-        </is>
-      </c>
-      <c r="AM272" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN272" t="b">
-        <v>1</v>
       </c>
       <c r="AO272" t="inlineStr">
         <is>
@@ -47850,6 +47756,245 @@
         </is>
       </c>
       <c r="BC272" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>haemophilus-influenzae</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>流感嗜血杆菌</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N273" t="n">
+        <v>0</v>
+      </c>
+      <c r="O273" t="n">
+        <v>0</v>
+      </c>
+      <c r="U273" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_103_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V273" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_103_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W273" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X273" t="inlineStr">
+        <is>
+          <t>Syst. H. influenzae-sykdom</t>
+        </is>
+      </c>
+      <c r="Y273" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z273" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA273" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB273" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC273" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD273" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE273" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF273" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG273" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH273" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI273" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ273" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK273" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic disease mapping.</t>
+        </is>
+      </c>
+      <c r="AM273" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN273" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO273" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP273" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ273" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR273" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS273" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_103_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT273" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU273" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV273" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW273" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX273" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY273" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ273" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA273" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB273" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC273" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -47971,7 +48116,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="10">
@@ -47981,7 +48126,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="11">
@@ -48033,7 +48178,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2421</v>
+        <v>2434</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d100/2026-2029.xlsx
+++ b/diseases/d100/2026-2029.xlsx
@@ -43139,13 +43139,13 @@
         </is>
       </c>
       <c r="N246" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O246" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R246" t="n">
-        <v>0.1238283078056854</v>
+        <v>0.1592078243215956</v>
       </c>
       <c r="S246" t="inlineStr">
         <is>
@@ -43303,10 +43303,10 @@
         </is>
       </c>
       <c r="N247" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O247" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U247" t="inlineStr">
         <is>
@@ -47664,13 +47664,13 @@
         </is>
       </c>
       <c r="N272" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O272" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R272" t="n">
-        <v>0</v>
+        <v>0.05306927477386519</v>
       </c>
       <c r="S272" t="inlineStr">
         <is>
@@ -47828,10 +47828,10 @@
         </is>
       </c>
       <c r="N273" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O273" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U273" t="inlineStr">
         <is>
@@ -48178,7 +48178,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2434</v>
+        <v>2439</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d100/2026-2029.xlsx
+++ b/diseases/d100/2026-2029.xlsx
@@ -46932,12 +46932,12 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -46962,12 +46962,12 @@
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N268" t="n">
@@ -46976,6 +46976,9 @@
       <c r="O268" t="n">
         <v>0</v>
       </c>
+      <c r="P268" t="n">
+        <v>0</v>
+      </c>
       <c r="R268" t="n">
         <v>0</v>
       </c>
@@ -46984,68 +46987,77 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA268" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO268" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP268" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR268" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS268" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ268" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS268" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B; SER_SG_HIST_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
       <c r="AT268" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU268" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV268" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW268" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX268" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY268" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ268" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA268" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB268" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC268" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -47072,17 +47084,17 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -47107,38 +47119,116 @@
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N269" t="n">
+        <v>0</v>
+      </c>
+      <c r="O269" t="n">
+        <v>0</v>
+      </c>
+      <c r="P269" t="n">
+        <v>0</v>
+      </c>
+      <c r="U269" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
+      <c r="V269" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
+      <c r="W269" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X269" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae type b</t>
+        </is>
+      </c>
+      <c r="Y269" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z269" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA269" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB269" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC269" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD269" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE269" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF269" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG269" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH269" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI269" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ269" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK269" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM269" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN269" t="b">
         <v>1</v>
       </c>
-      <c r="O269" t="n">
-        <v>1</v>
-      </c>
-      <c r="R269" t="n">
-        <v>0.01778809170864137</v>
-      </c>
-      <c r="S269" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U269" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1459</t>
-        </is>
-      </c>
-      <c r="AA269" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO269" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -47146,22 +47236,17 @@
       </c>
       <c r="AP269" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ269" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR269" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS269" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1459</t>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B; SER_SG_HIST_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
         </is>
       </c>
       <c r="AT269" t="n">
@@ -47169,47 +47254,47 @@
       </c>
       <c r="AU269" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV269" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW269" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX269" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY269" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ269" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA269" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB269" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC269" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -47236,17 +47321,17 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -47280,175 +47365,81 @@
         </is>
       </c>
       <c r="N270" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O270" t="n">
-        <v>1</v>
-      </c>
-      <c r="U270" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1459</t>
-        </is>
-      </c>
-      <c r="V270" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1459</t>
-        </is>
-      </c>
-      <c r="W270" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X270" t="inlineStr">
-        <is>
-          <t>Haemophilus influenzae,total</t>
-        </is>
-      </c>
-      <c r="Y270" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z270" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA270" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB270" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC270" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD270" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="R270" t="n">
+        <v>0</v>
+      </c>
+      <c r="S270" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO270" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP270" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR270" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS270" t="inlineStr"/>
+      <c r="AT270" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU270" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV270" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE270" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF270" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG270" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH270" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI270" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ270" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK270" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Use the THL reported total; serotype child rows remain independent unprojected series.</t>
-        </is>
-      </c>
-      <c r="AM270" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN270" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO270" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP270" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ270" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR270" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS270" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1459</t>
-        </is>
-      </c>
-      <c r="AT270" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU270" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV270" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW270" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX270" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY270" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ270" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA270" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB270" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC270" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -47480,12 +47471,12 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -47519,81 +47510,100 @@
         </is>
       </c>
       <c r="N271" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O271" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R271" t="n">
-        <v>0</v>
+        <v>0.01778809170864137</v>
       </c>
       <c r="S271" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U271" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1459</t>
+        </is>
+      </c>
+      <c r="AA271" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO271" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP271" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ271" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR271" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS271" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS271" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1459</t>
+        </is>
+      </c>
       <c r="AT271" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU271" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV271" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW271" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX271" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY271" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ271" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA271" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB271" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC271" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -47620,17 +47630,17 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -47664,22 +47674,39 @@
         </is>
       </c>
       <c r="N272" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O272" t="n">
-        <v>3</v>
-      </c>
-      <c r="R272" t="n">
-        <v>0.05306927477386519</v>
-      </c>
-      <c r="S272" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="U272" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1459</t>
+        </is>
+      </c>
+      <c r="V272" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1459</t>
+        </is>
+      </c>
+      <c r="W272" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X272" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae,total</t>
+        </is>
+      </c>
+      <c r="Y272" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z272" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA272" t="inlineStr">
@@ -47687,6 +47714,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB272" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC272" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD272" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE272" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF272" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG272" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH272" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI272" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ272" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK272" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Use the THL reported total; serotype child rows remain independent unprojected series.</t>
+        </is>
+      </c>
+      <c r="AM272" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN272" t="b">
+        <v>1</v>
+      </c>
       <c r="AO272" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -47699,7 +47784,7 @@
       </c>
       <c r="AQ272" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR272" t="inlineStr">
@@ -47709,7 +47794,7 @@
       </c>
       <c r="AS272" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="AT272" t="n">
@@ -47717,47 +47802,47 @@
       </c>
       <c r="AU272" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV272" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW272" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX272" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY272" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ272" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA272" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB272" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC272" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -47784,219 +47869,673 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>流感嗜血杆菌</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N273" t="n">
+        <v>0</v>
+      </c>
+      <c r="O273" t="n">
+        <v>0</v>
+      </c>
+      <c r="R273" t="n">
+        <v>0</v>
+      </c>
+      <c r="S273" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO273" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP273" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR273" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS273" t="inlineStr"/>
+      <c r="AT273" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU273" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV273" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW273" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX273" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY273" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ273" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA273" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB273" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC273" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>haemophilus-influenzae</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>流感嗜血杆菌</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N274" t="n">
+        <v>3</v>
+      </c>
+      <c r="O274" t="n">
+        <v>3</v>
+      </c>
+      <c r="R274" t="n">
+        <v>0.05306927477386519</v>
+      </c>
+      <c r="S274" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U274" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_103_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA274" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO274" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP274" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ274" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR274" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS274" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_103_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT274" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU274" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV274" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW274" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX274" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY274" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ274" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA274" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB274" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC274" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>haemophilus-influenzae</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
           <t>source_series_observation</t>
         </is>
       </c>
-      <c r="F273" t="inlineStr">
+      <c r="F275" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G273" t="inlineStr">
+      <c r="G275" t="inlineStr">
         <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="H273" t="inlineStr">
-        <is>
-          <t>D100</t>
-        </is>
-      </c>
-      <c r="I273" t="inlineStr">
-        <is>
-          <t>Haemophilus influenzae</t>
-        </is>
-      </c>
-      <c r="J273" t="inlineStr">
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
         <is>
           <t>流感嗜血杆菌</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr">
+      <c r="K275" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L273" t="inlineStr">
+      <c r="L275" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="M273" t="inlineStr">
+      <c r="M275" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N273" t="n">
+      <c r="N275" t="n">
         <v>3</v>
       </c>
-      <c r="O273" t="n">
+      <c r="O275" t="n">
         <v>3</v>
       </c>
-      <c r="U273" t="inlineStr">
+      <c r="U275" t="inlineStr">
         <is>
           <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
-      <c r="V273" t="inlineStr">
+      <c r="V275" t="inlineStr">
         <is>
           <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
-      <c r="W273" t="inlineStr">
+      <c r="W275" t="inlineStr">
         <is>
           <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
-      <c r="X273" t="inlineStr">
+      <c r="X275" t="inlineStr">
         <is>
           <t>Syst. H. influenzae-sykdom</t>
         </is>
       </c>
-      <c r="Y273" t="inlineStr">
+      <c r="Y275" t="inlineStr">
         <is>
           <t>case_notifications</t>
         </is>
       </c>
-      <c r="Z273" t="inlineStr">
+      <c r="Z275" t="inlineStr">
         <is>
           <t>national_notifiable_disease_registry</t>
         </is>
       </c>
-      <c r="AA273" t="inlineStr">
+      <c r="AA275" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB273" t="inlineStr">
+      <c r="AB275" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="AC273" t="inlineStr">
+      <c r="AC275" t="inlineStr">
         <is>
           <t>country:NO:national</t>
         </is>
       </c>
-      <c r="AD273" t="inlineStr">
+      <c r="AD275" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE273" t="inlineStr">
+      <c r="AE275" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="AF273" t="inlineStr">
+      <c r="AF275" t="inlineStr">
         <is>
           <t>conditional</t>
         </is>
       </c>
-      <c r="AG273" t="inlineStr">
+      <c r="AG275" t="inlineStr">
         <is>
           <t>non_additive</t>
         </is>
       </c>
-      <c r="AH273" t="inlineStr">
+      <c r="AH275" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="AI273" t="inlineStr">
+      <c r="AI275" t="inlineStr">
         <is>
           <t>missing_is_unknown</t>
         </is>
       </c>
-      <c r="AJ273" t="inlineStr">
+      <c r="AJ275" t="inlineStr">
         <is>
           <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
-      <c r="AK273" t="inlineStr">
+      <c r="AK275" t="inlineStr">
         <is>
           <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic disease mapping.</t>
         </is>
       </c>
-      <c r="AM273" t="inlineStr">
+      <c r="AM275" t="inlineStr">
         <is>
           <t>provisional; raw; revised</t>
         </is>
       </c>
-      <c r="AN273" t="b">
+      <c r="AN275" t="b">
         <v>1</v>
       </c>
-      <c r="AO273" t="inlineStr">
+      <c r="AO275" t="inlineStr">
         <is>
           <t>series_registry</t>
         </is>
       </c>
-      <c r="AP273" t="inlineStr">
+      <c r="AP275" t="inlineStr">
         <is>
           <t>representative_series</t>
         </is>
       </c>
-      <c r="AQ273" t="inlineStr">
+      <c r="AQ275" t="inlineStr">
         <is>
           <t>parity</t>
         </is>
       </c>
-      <c r="AR273" t="inlineStr">
+      <c r="AR275" t="inlineStr">
         <is>
           <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
-      <c r="AS273" t="inlineStr">
+      <c r="AS275" t="inlineStr">
         <is>
           <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
-      <c r="AT273" t="n">
+      <c r="AT275" t="n">
         <v>2</v>
       </c>
-      <c r="AU273" t="inlineStr">
+      <c r="AU275" t="inlineStr">
         <is>
           <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
-      <c r="AV273" t="inlineStr">
+      <c r="AV275" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW273" t="inlineStr">
+      <c r="AW275" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX273" t="inlineStr">
+      <c r="AX275" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY273" t="inlineStr">
+      <c r="AY275" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ273" t="inlineStr">
+      <c r="AZ275" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA273" t="inlineStr">
+      <c r="BA275" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB273" t="inlineStr">
+      <c r="BB275" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC273" t="inlineStr">
+      <c r="BC275" t="inlineStr">
         <is>
           <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>haemophilus-influenzae</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>流感嗜血杆菌</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N276" t="n">
+        <v>21</v>
+      </c>
+      <c r="O276" t="n">
+        <v>21</v>
+      </c>
+      <c r="R276" t="n">
+        <v>0.006016580078815709</v>
+      </c>
+      <c r="S276" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO276" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP276" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR276" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS276" t="inlineStr"/>
+      <c r="AT276" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU276" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV276" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW276" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX276" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY276" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ276" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA276" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB276" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC276" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -48033,7 +48572,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -48116,7 +48655,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="10">
@@ -48126,7 +48665,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11">
@@ -48146,7 +48685,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13">
@@ -48178,7 +48717,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2439</v>
+        <v>2460</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d100/2026-2029.xlsx
+++ b/diseases/d100/2026-2029.xlsx
@@ -47900,13 +47900,13 @@
         </is>
       </c>
       <c r="N273" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O273" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R273" t="n">
-        <v>0.01778809170864137</v>
+        <v>0.03557618341728275</v>
       </c>
       <c r="S273" t="inlineStr">
         <is>
@@ -48064,10 +48064,10 @@
         </is>
       </c>
       <c r="N274" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O274" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U274" t="inlineStr">
         <is>
@@ -48926,6 +48926,151 @@
       <c r="BC278" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>haemophilus-influenzae</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>流感嗜血杆菌</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N279" t="n">
+        <v>6</v>
+      </c>
+      <c r="O279" t="n">
+        <v>6</v>
+      </c>
+      <c r="R279" t="n">
+        <v>0.004900850445394598</v>
+      </c>
+      <c r="S279" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO279" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP279" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR279" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS279" t="inlineStr"/>
+      <c r="AT279" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU279" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV279" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW279" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX279" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY279" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ279" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA279" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB279" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC279" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -48962,7 +49107,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -49045,7 +49190,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="10">
@@ -49055,7 +49200,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="11">
@@ -49107,7 +49252,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2492</v>
+        <v>2499</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d100/2026-2029.xlsx
+++ b/diseases/d100/2026-2029.xlsx
@@ -43893,12 +43893,12 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -43932,13 +43932,13 @@
         </is>
       </c>
       <c r="N250" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="O250" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R250" t="n">
-        <v>0.2242771302788003</v>
+        <v>0</v>
       </c>
       <c r="S250" t="inlineStr">
         <is>
@@ -43947,7 +43947,7 @@
       </c>
       <c r="U250" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HAEMOPHILUS_INVASIVE</t>
+          <t>SER_NZ_HAEMOPHILUS_INFLUENZAE_TYPE_B_MONTHLY</t>
         </is>
       </c>
       <c r="AA250" t="inlineStr">
@@ -43962,7 +43962,7 @@
       </c>
       <c r="AP250" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ250" t="inlineStr">
@@ -43970,62 +43970,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR250" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS250" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HAEMOPHILUS_INVASIVE</t>
+          <t>SER_NZ_HAEMOPHILUS_INFLUENZAE_TYPE_B_MONTHLY</t>
         </is>
       </c>
       <c r="AT250" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU250" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV250" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ250" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA250" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB250" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC250" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -44057,12 +44052,12 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -44096,29 +44091,29 @@
         </is>
       </c>
       <c r="N251" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="O251" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U251" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HAEMOPHILUS_INVASIVE</t>
+          <t>SER_NZ_HAEMOPHILUS_INFLUENZAE_TYPE_B_MONTHLY</t>
         </is>
       </c>
       <c r="V251" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HAEMOPHILUS_INVASIVE</t>
+          <t>SER_NZ_HAEMOPHILUS_INFLUENZAE_TYPE_B_MONTHLY</t>
         </is>
       </c>
       <c r="W251" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X251" t="inlineStr">
         <is>
-          <t>Invasiv infektion med Haemophilus influenzae</t>
+          <t>Haemophilus influenzae type b</t>
         </is>
       </c>
       <c r="Y251" t="inlineStr">
@@ -44128,7 +44123,7 @@
       </c>
       <c r="Z251" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA251" t="inlineStr">
@@ -44143,7 +44138,7 @@
       </c>
       <c r="AC251" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD251" t="inlineStr">
@@ -44153,7 +44148,7 @@
       </c>
       <c r="AE251" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>narrower</t>
         </is>
       </c>
       <c r="AF251" t="inlineStr">
@@ -44178,17 +44173,17 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; Source is invasive disease and is not assumed to be type b only.</t>
+          <t>New Zealand PHF Science monthly Haemophilus influenzae type b notifications; the serotype-qualified source series is narrower than unqualified D100.</t>
         </is>
       </c>
       <c r="AM251" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN251" t="b">
@@ -44201,7 +44196,7 @@
       </c>
       <c r="AP251" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ251" t="inlineStr">
@@ -44209,62 +44204,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR251" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS251" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HAEMOPHILUS_INVASIVE</t>
+          <t>SER_NZ_HAEMOPHILUS_INFLUENZAE_TYPE_B_MONTHLY</t>
         </is>
       </c>
       <c r="AT251" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU251" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV251" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW251" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ251" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA251" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB251" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC251" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -44296,12 +44286,12 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -44335,81 +44325,100 @@
         </is>
       </c>
       <c r="N252" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="O252" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="R252" t="n">
-        <v>0.009454625838138971</v>
+        <v>0.2242771302788003</v>
       </c>
       <c r="S252" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U252" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HAEMOPHILUS_INVASIVE</t>
+        </is>
+      </c>
+      <c r="AA252" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO252" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP252" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ252" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR252" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS252" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS252" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HAEMOPHILUS_INVASIVE</t>
+        </is>
+      </c>
       <c r="AT252" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU252" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV252" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW252" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ252" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA252" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB252" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC252" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -44436,17 +44445,17 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -44471,7 +44480,7 @@
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M253" t="inlineStr">
@@ -44480,81 +44489,175 @@
         </is>
       </c>
       <c r="N253" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="O253" t="n">
-        <v>6</v>
-      </c>
-      <c r="R253" t="n">
-        <v>0.004900850445394598</v>
-      </c>
-      <c r="S253" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>24</v>
+      </c>
+      <c r="U253" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HAEMOPHILUS_INVASIVE</t>
+        </is>
+      </c>
+      <c r="V253" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HAEMOPHILUS_INVASIVE</t>
+        </is>
+      </c>
+      <c r="W253" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X253" t="inlineStr">
+        <is>
+          <t>Invasiv infektion med Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="Y253" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z253" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA253" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB253" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC253" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD253" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE253" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF253" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG253" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH253" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI253" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ253" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK253" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; Source is invasive disease and is not assumed to be type b only.</t>
+        </is>
+      </c>
+      <c r="AM253" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN253" t="b">
+        <v>1</v>
       </c>
       <c r="AO253" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP253" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ253" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR253" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS253" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS253" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HAEMOPHILUS_INVASIVE</t>
+        </is>
+      </c>
       <c r="AT253" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU253" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV253" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ253" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA253" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB253" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC253" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -44586,12 +44689,12 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -44616,7 +44719,7 @@
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M254" t="inlineStr">
@@ -44625,93 +44728,81 @@
         </is>
       </c>
       <c r="N254" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="O254" t="n">
-        <v>0</v>
-      </c>
-      <c r="P254" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="R254" t="n">
-        <v>0</v>
+        <v>0.009454625838138971</v>
       </c>
       <c r="S254" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA254" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO254" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP254" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ254" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS254" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B; SER_SG_HIST_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR254" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS254" t="inlineStr"/>
       <c r="AT254" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU254" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV254" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW254" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ254" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA254" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB254" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC254" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -44738,17 +44829,17 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -44782,173 +44873,81 @@
         </is>
       </c>
       <c r="N255" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O255" t="n">
-        <v>0</v>
-      </c>
-      <c r="P255" t="n">
-        <v>0</v>
-      </c>
-      <c r="U255" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
-      <c r="V255" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
-      <c r="W255" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X255" t="inlineStr">
-        <is>
-          <t>Haemophilus influenzae type b</t>
-        </is>
-      </c>
-      <c r="Y255" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z255" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA255" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB255" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC255" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD255" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE255" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF255" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG255" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH255" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI255" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ255" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK255" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM255" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN255" t="b">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="R255" t="n">
+        <v>0.004900850445394598</v>
+      </c>
+      <c r="S255" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO255" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP255" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ255" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS255" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B; SER_SG_HIST_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR255" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS255" t="inlineStr"/>
       <c r="AT255" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU255" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV255" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW255" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX255" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY255" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ255" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA255" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB255" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC255" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -44980,12 +44979,12 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -45010,7 +45009,7 @@
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M256" t="inlineStr">
@@ -45019,81 +45018,93 @@
         </is>
       </c>
       <c r="N256" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="O256" t="n">
-        <v>41</v>
+        <v>0</v>
+      </c>
+      <c r="P256" t="n">
+        <v>0</v>
       </c>
       <c r="R256" t="n">
-        <v>0.01174665634435448</v>
+        <v>0</v>
       </c>
       <c r="S256" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA256" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO256" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP256" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR256" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS256" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ256" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS256" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B; SER_SG_HIST_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
       <c r="AT256" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU256" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV256" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW256" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY256" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ256" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA256" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB256" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC256" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -45120,17 +45131,17 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -45155,7 +45166,7 @@
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M257" t="inlineStr">
@@ -45164,81 +45175,173 @@
         </is>
       </c>
       <c r="N257" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O257" t="n">
-        <v>6</v>
-      </c>
-      <c r="R257" t="n">
-        <v>0.004900850445394598</v>
-      </c>
-      <c r="S257" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="P257" t="n">
+        <v>0</v>
+      </c>
+      <c r="U257" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
+      <c r="V257" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
+      <c r="W257" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X257" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae type b</t>
+        </is>
+      </c>
+      <c r="Y257" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z257" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA257" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB257" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC257" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD257" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE257" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF257" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG257" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH257" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI257" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ257" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK257" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM257" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN257" t="b">
+        <v>1</v>
       </c>
       <c r="AO257" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP257" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR257" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS257" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ257" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS257" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B; SER_SG_HIST_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
       <c r="AT257" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU257" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV257" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW257" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX257" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY257" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ257" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA257" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB257" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC257" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -45270,12 +45373,12 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -45300,7 +45403,7 @@
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M258" t="inlineStr">
@@ -45309,93 +45412,81 @@
         </is>
       </c>
       <c r="N258" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="O258" t="n">
-        <v>0</v>
-      </c>
-      <c r="P258" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="R258" t="n">
-        <v>0</v>
+        <v>0.01174665634435448</v>
       </c>
       <c r="S258" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA258" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO258" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP258" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ258" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS258" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B; SER_SG_HIST_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR258" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS258" t="inlineStr"/>
       <c r="AT258" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU258" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV258" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW258" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX258" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY258" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ258" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA258" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB258" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC258" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -45422,17 +45513,17 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -45466,173 +45557,81 @@
         </is>
       </c>
       <c r="N259" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O259" t="n">
-        <v>0</v>
-      </c>
-      <c r="P259" t="n">
-        <v>0</v>
-      </c>
-      <c r="U259" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
-      <c r="V259" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
-      <c r="W259" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X259" t="inlineStr">
-        <is>
-          <t>Haemophilus influenzae type b</t>
-        </is>
-      </c>
-      <c r="Y259" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z259" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA259" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB259" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC259" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD259" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE259" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF259" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG259" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH259" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI259" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ259" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK259" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM259" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN259" t="b">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="R259" t="n">
+        <v>0.004900850445394598</v>
+      </c>
+      <c r="S259" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO259" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP259" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ259" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS259" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B; SER_SG_HIST_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR259" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS259" t="inlineStr"/>
       <c r="AT259" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU259" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV259" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW259" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX259" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY259" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ259" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA259" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB259" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC259" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -45664,12 +45663,12 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -45694,7 +45693,7 @@
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M260" t="inlineStr">
@@ -45703,81 +45702,93 @@
         </is>
       </c>
       <c r="N260" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="O260" t="n">
-        <v>38</v>
+        <v>0</v>
+      </c>
+      <c r="P260" t="n">
+        <v>0</v>
       </c>
       <c r="R260" t="n">
-        <v>0.01088714490452366</v>
+        <v>0</v>
       </c>
       <c r="S260" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA260" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO260" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP260" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR260" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS260" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ260" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS260" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B; SER_SG_HIST_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
       <c r="AT260" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU260" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV260" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW260" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY260" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ260" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA260" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB260" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC260" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -45804,17 +45815,17 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -45839,7 +45850,7 @@
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M261" t="inlineStr">
@@ -45848,81 +45859,173 @@
         </is>
       </c>
       <c r="N261" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O261" t="n">
-        <v>14</v>
-      </c>
-      <c r="R261" t="n">
-        <v>0.01143531770592073</v>
-      </c>
-      <c r="S261" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="P261" t="n">
+        <v>0</v>
+      </c>
+      <c r="U261" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
+      <c r="V261" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
+      <c r="W261" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X261" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae type b</t>
+        </is>
+      </c>
+      <c r="Y261" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z261" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA261" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB261" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC261" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD261" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE261" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF261" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG261" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH261" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI261" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ261" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK261" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM261" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN261" t="b">
+        <v>1</v>
       </c>
       <c r="AO261" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP261" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR261" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS261" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ261" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS261" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B; SER_SG_HIST_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
       <c r="AT261" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU261" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV261" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW261" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX261" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY261" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ261" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA261" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB261" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC261" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -45954,12 +46057,12 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -45984,7 +46087,7 @@
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M262" t="inlineStr">
@@ -45993,93 +46096,81 @@
         </is>
       </c>
       <c r="N262" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="O262" t="n">
-        <v>0</v>
-      </c>
-      <c r="P262" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="R262" t="n">
-        <v>0</v>
+        <v>0.01088714490452366</v>
       </c>
       <c r="S262" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA262" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO262" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP262" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ262" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS262" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B; SER_SG_HIST_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR262" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS262" t="inlineStr"/>
       <c r="AT262" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU262" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV262" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW262" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX262" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY262" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ262" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA262" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB262" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC262" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -46106,17 +46197,17 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -46150,173 +46241,81 @@
         </is>
       </c>
       <c r="N263" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O263" t="n">
-        <v>0</v>
-      </c>
-      <c r="P263" t="n">
-        <v>0</v>
-      </c>
-      <c r="U263" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
-      <c r="V263" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
-      <c r="W263" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X263" t="inlineStr">
-        <is>
-          <t>Haemophilus influenzae type b</t>
-        </is>
-      </c>
-      <c r="Y263" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z263" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA263" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB263" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC263" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD263" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE263" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF263" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG263" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH263" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI263" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ263" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK263" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM263" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN263" t="b">
-        <v>1</v>
+        <v>14</v>
+      </c>
+      <c r="R263" t="n">
+        <v>0.01143531770592073</v>
+      </c>
+      <c r="S263" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO263" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP263" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ263" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS263" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B; SER_SG_HIST_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR263" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS263" t="inlineStr"/>
       <c r="AT263" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU263" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV263" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW263" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX263" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY263" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ263" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA263" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB263" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC263" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -46348,12 +46347,12 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -46378,7 +46377,7 @@
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M264" t="inlineStr">
@@ -46387,81 +46386,93 @@
         </is>
       </c>
       <c r="N264" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="O264" t="n">
-        <v>30</v>
+        <v>0</v>
+      </c>
+      <c r="P264" t="n">
+        <v>0</v>
       </c>
       <c r="R264" t="n">
-        <v>0.008595114398308155</v>
+        <v>0</v>
       </c>
       <c r="S264" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA264" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO264" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP264" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR264" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS264" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ264" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS264" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B; SER_SG_HIST_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
       <c r="AT264" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU264" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV264" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW264" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX264" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY264" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ264" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA264" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB264" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC264" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -46488,17 +46499,17 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -46523,7 +46534,7 @@
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M265" t="inlineStr">
@@ -46532,81 +46543,173 @@
         </is>
       </c>
       <c r="N265" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O265" t="n">
-        <v>8</v>
-      </c>
-      <c r="R265" t="n">
-        <v>0.00653446726052613</v>
-      </c>
-      <c r="S265" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="P265" t="n">
+        <v>0</v>
+      </c>
+      <c r="U265" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
+      <c r="V265" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
+      <c r="W265" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X265" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae type b</t>
+        </is>
+      </c>
+      <c r="Y265" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z265" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA265" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB265" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC265" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD265" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE265" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF265" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG265" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH265" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI265" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ265" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK265" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM265" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN265" t="b">
+        <v>1</v>
       </c>
       <c r="AO265" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP265" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR265" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS265" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ265" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS265" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B; SER_SG_HIST_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
       <c r="AT265" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU265" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV265" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW265" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX265" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY265" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ265" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA265" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB265" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC265" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -46638,12 +46741,12 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -46668,7 +46771,7 @@
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M266" t="inlineStr">
@@ -46677,93 +46780,81 @@
         </is>
       </c>
       <c r="N266" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="O266" t="n">
-        <v>0</v>
-      </c>
-      <c r="P266" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="R266" t="n">
-        <v>0</v>
+        <v>0.008595114398308155</v>
       </c>
       <c r="S266" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA266" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO266" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP266" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ266" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS266" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B; SER_SG_HIST_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR266" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS266" t="inlineStr"/>
       <c r="AT266" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU266" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV266" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW266" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX266" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY266" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ266" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA266" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB266" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC266" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -46790,17 +46881,17 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -46834,173 +46925,81 @@
         </is>
       </c>
       <c r="N267" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O267" t="n">
-        <v>0</v>
-      </c>
-      <c r="P267" t="n">
-        <v>0</v>
-      </c>
-      <c r="U267" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
-      <c r="V267" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
-      <c r="W267" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X267" t="inlineStr">
-        <is>
-          <t>Haemophilus influenzae type b</t>
-        </is>
-      </c>
-      <c r="Y267" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z267" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA267" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB267" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC267" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD267" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE267" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF267" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG267" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH267" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI267" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ267" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK267" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM267" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN267" t="b">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="R267" t="n">
+        <v>0.00653446726052613</v>
+      </c>
+      <c r="S267" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO267" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP267" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ267" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS267" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B; SER_SG_HIST_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR267" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS267" t="inlineStr"/>
       <c r="AT267" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU267" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV267" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW267" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX267" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY267" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ267" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA267" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB267" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC267" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -47032,12 +47031,12 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -47062,7 +47061,7 @@
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M268" t="inlineStr">
@@ -47071,81 +47070,93 @@
         </is>
       </c>
       <c r="N268" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="O268" t="n">
-        <v>36</v>
+        <v>0</v>
+      </c>
+      <c r="P268" t="n">
+        <v>0</v>
       </c>
       <c r="R268" t="n">
-        <v>0.01031413727796979</v>
+        <v>0</v>
       </c>
       <c r="S268" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA268" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO268" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP268" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR268" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS268" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ268" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS268" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B; SER_SG_HIST_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
       <c r="AT268" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU268" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV268" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW268" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX268" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY268" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ268" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA268" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB268" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC268" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -47172,17 +47183,17 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -47207,7 +47218,7 @@
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M269" t="inlineStr">
@@ -47216,81 +47227,173 @@
         </is>
       </c>
       <c r="N269" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O269" t="n">
-        <v>12</v>
-      </c>
-      <c r="R269" t="n">
-        <v>0.009801700890789196</v>
-      </c>
-      <c r="S269" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="P269" t="n">
+        <v>0</v>
+      </c>
+      <c r="U269" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
+      <c r="V269" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
+      <c r="W269" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X269" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae type b</t>
+        </is>
+      </c>
+      <c r="Y269" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z269" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA269" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB269" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC269" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD269" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE269" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF269" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG269" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH269" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI269" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ269" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK269" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM269" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN269" t="b">
+        <v>1</v>
       </c>
       <c r="AO269" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP269" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR269" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS269" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ269" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS269" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B; SER_SG_HIST_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
       <c r="AT269" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU269" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV269" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW269" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX269" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY269" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ269" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA269" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB269" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC269" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -47322,12 +47425,12 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -47352,7 +47455,7 @@
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M270" t="inlineStr">
@@ -47361,93 +47464,81 @@
         </is>
       </c>
       <c r="N270" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="O270" t="n">
-        <v>0</v>
-      </c>
-      <c r="P270" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="R270" t="n">
-        <v>0</v>
+        <v>0.01031413727796979</v>
       </c>
       <c r="S270" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA270" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO270" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP270" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ270" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS270" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B; SER_SG_HIST_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR270" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS270" t="inlineStr"/>
       <c r="AT270" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU270" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV270" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW270" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX270" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY270" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ270" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA270" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB270" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC270" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -47474,17 +47565,17 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -47518,173 +47609,81 @@
         </is>
       </c>
       <c r="N271" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O271" t="n">
-        <v>0</v>
-      </c>
-      <c r="P271" t="n">
-        <v>0</v>
-      </c>
-      <c r="U271" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
-      <c r="V271" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
-      <c r="W271" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X271" t="inlineStr">
-        <is>
-          <t>Haemophilus influenzae type b</t>
-        </is>
-      </c>
-      <c r="Y271" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z271" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA271" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB271" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC271" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD271" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE271" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF271" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG271" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH271" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI271" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ271" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK271" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM271" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN271" t="b">
-        <v>1</v>
+        <v>12</v>
+      </c>
+      <c r="R271" t="n">
+        <v>0.009801700890789196</v>
+      </c>
+      <c r="S271" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO271" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP271" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ271" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS271" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B; SER_SG_HIST_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR271" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS271" t="inlineStr"/>
       <c r="AT271" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU271" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV271" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW271" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX271" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY271" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ271" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA271" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB271" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC271" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -47716,12 +47715,12 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -47746,12 +47745,12 @@
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N272" t="n">
@@ -47760,6 +47759,9 @@
       <c r="O272" t="n">
         <v>0</v>
       </c>
+      <c r="P272" t="n">
+        <v>0</v>
+      </c>
       <c r="R272" t="n">
         <v>0</v>
       </c>
@@ -47768,68 +47770,77 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA272" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO272" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP272" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR272" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS272" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ272" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS272" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B; SER_SG_HIST_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
       <c r="AT272" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU272" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV272" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW272" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX272" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY272" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ272" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA272" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB272" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC272" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -47856,17 +47867,17 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -47891,37 +47902,115 @@
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N273" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O273" t="n">
-        <v>2</v>
-      </c>
-      <c r="R273" t="n">
-        <v>0.03557618341728275</v>
-      </c>
-      <c r="S273" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="P273" t="n">
+        <v>0</v>
       </c>
       <c r="U273" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1459</t>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
+      <c r="V273" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
+      <c r="W273" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X273" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae type b</t>
+        </is>
+      </c>
+      <c r="Y273" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z273" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA273" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB273" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC273" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD273" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE273" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF273" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG273" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH273" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI273" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ273" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK273" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM273" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN273" t="b">
+        <v>1</v>
       </c>
       <c r="AO273" t="inlineStr">
         <is>
@@ -47930,22 +48019,17 @@
       </c>
       <c r="AP273" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ273" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR273" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS273" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1459</t>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B; SER_SG_HIST_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
         </is>
       </c>
       <c r="AT273" t="n">
@@ -47953,47 +48037,47 @@
       </c>
       <c r="AU273" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV273" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW273" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX273" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY273" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ273" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA273" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB273" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC273" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -48020,17 +48104,17 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -48064,175 +48148,81 @@
         </is>
       </c>
       <c r="N274" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O274" t="n">
-        <v>2</v>
-      </c>
-      <c r="U274" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1459</t>
-        </is>
-      </c>
-      <c r="V274" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1459</t>
-        </is>
-      </c>
-      <c r="W274" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X274" t="inlineStr">
-        <is>
-          <t>Haemophilus influenzae,total</t>
-        </is>
-      </c>
-      <c r="Y274" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z274" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA274" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB274" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC274" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD274" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="R274" t="n">
+        <v>0</v>
+      </c>
+      <c r="S274" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO274" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP274" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR274" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS274" t="inlineStr"/>
+      <c r="AT274" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU274" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV274" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE274" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF274" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG274" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH274" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI274" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ274" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK274" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Use the THL reported total; serotype child rows remain independent unprojected series.</t>
-        </is>
-      </c>
-      <c r="AM274" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN274" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO274" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP274" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ274" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR274" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS274" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1459</t>
-        </is>
-      </c>
-      <c r="AT274" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU274" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV274" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW274" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX274" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY274" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ274" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA274" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB274" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC274" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -48264,12 +48254,12 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -48303,81 +48293,100 @@
         </is>
       </c>
       <c r="N275" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O275" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R275" t="n">
-        <v>0</v>
+        <v>0.03557618341728275</v>
       </c>
       <c r="S275" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U275" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1459</t>
+        </is>
+      </c>
+      <c r="AA275" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO275" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP275" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ275" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR275" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS275" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS275" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1459</t>
+        </is>
+      </c>
       <c r="AT275" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU275" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV275" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW275" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX275" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY275" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ275" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA275" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB275" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC275" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -48404,17 +48413,17 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -48448,22 +48457,39 @@
         </is>
       </c>
       <c r="N276" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O276" t="n">
-        <v>3</v>
-      </c>
-      <c r="R276" t="n">
-        <v>0.05306927477386519</v>
-      </c>
-      <c r="S276" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
       </c>
       <c r="U276" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1459</t>
+        </is>
+      </c>
+      <c r="V276" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1459</t>
+        </is>
+      </c>
+      <c r="W276" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X276" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae,total</t>
+        </is>
+      </c>
+      <c r="Y276" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z276" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA276" t="inlineStr">
@@ -48471,6 +48497,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB276" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC276" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD276" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE276" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF276" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG276" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH276" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI276" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ276" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK276" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Use the THL reported total; serotype child rows remain independent unprojected series.</t>
+        </is>
+      </c>
+      <c r="AM276" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN276" t="b">
+        <v>1</v>
+      </c>
       <c r="AO276" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -48483,7 +48567,7 @@
       </c>
       <c r="AQ276" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR276" t="inlineStr">
@@ -48493,7 +48577,7 @@
       </c>
       <c r="AS276" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="AT276" t="n">
@@ -48501,47 +48585,47 @@
       </c>
       <c r="AU276" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV276" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW276" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX276" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY276" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ276" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA276" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB276" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC276" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -48568,17 +48652,17 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -48612,175 +48696,81 @@
         </is>
       </c>
       <c r="N277" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O277" t="n">
-        <v>3</v>
-      </c>
-      <c r="U277" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V277" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W277" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X277" t="inlineStr">
-        <is>
-          <t>Syst. H. influenzae-sykdom</t>
-        </is>
-      </c>
-      <c r="Y277" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z277" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA277" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB277" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC277" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD277" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE277" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF277" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG277" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH277" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI277" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ277" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK277" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic disease mapping.</t>
-        </is>
-      </c>
-      <c r="AM277" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN277" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R277" t="n">
+        <v>0</v>
+      </c>
+      <c r="S277" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO277" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP277" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ277" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR277" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS277" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS277" t="inlineStr"/>
       <c r="AT277" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU277" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV277" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW277" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX277" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY277" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ277" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA277" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB277" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC277" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -48812,12 +48802,12 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -48842,7 +48832,7 @@
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M278" t="inlineStr">
@@ -48851,81 +48841,100 @@
         </is>
       </c>
       <c r="N278" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="O278" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="R278" t="n">
-        <v>0.006016580078815709</v>
+        <v>0.05306927477386519</v>
       </c>
       <c r="S278" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U278" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_103_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA278" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO278" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP278" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ278" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR278" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS278" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS278" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_103_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT278" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU278" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV278" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW278" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX278" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY278" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ278" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA278" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB278" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC278" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -48952,123 +48961,507 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>流感嗜血杆菌</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N279" t="n">
+        <v>3</v>
+      </c>
+      <c r="O279" t="n">
+        <v>3</v>
+      </c>
+      <c r="U279" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_103_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V279" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_103_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W279" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X279" t="inlineStr">
+        <is>
+          <t>Syst. H. influenzae-sykdom</t>
+        </is>
+      </c>
+      <c r="Y279" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z279" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA279" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB279" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC279" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD279" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE279" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF279" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG279" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH279" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI279" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ279" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK279" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic disease mapping.</t>
+        </is>
+      </c>
+      <c r="AM279" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN279" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO279" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP279" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ279" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR279" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS279" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_103_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT279" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU279" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV279" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW279" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX279" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY279" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ279" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA279" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB279" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC279" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>haemophilus-influenzae</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
           <t>public_projection</t>
         </is>
       </c>
-      <c r="F279" t="inlineStr">
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>流感嗜血杆菌</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N280" t="n">
+        <v>21</v>
+      </c>
+      <c r="O280" t="n">
+        <v>21</v>
+      </c>
+      <c r="R280" t="n">
+        <v>0.006016580078815709</v>
+      </c>
+      <c r="S280" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO280" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP280" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR280" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS280" t="inlineStr"/>
+      <c r="AT280" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU280" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV280" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW280" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX280" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY280" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ280" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA280" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB280" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC280" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>haemophilus-influenzae</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
         <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="G279" t="inlineStr">
+      <c r="G281" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="H279" t="inlineStr">
-        <is>
-          <t>D100</t>
-        </is>
-      </c>
-      <c r="I279" t="inlineStr">
-        <is>
-          <t>Haemophilus influenzae</t>
-        </is>
-      </c>
-      <c r="J279" t="inlineStr">
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
         <is>
           <t>流感嗜血杆菌</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr">
+      <c r="K281" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L279" t="inlineStr">
+      <c r="L281" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="M279" t="inlineStr">
+      <c r="M281" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N279" t="n">
+      <c r="N281" t="n">
         <v>6</v>
       </c>
-      <c r="O279" t="n">
+      <c r="O281" t="n">
         <v>6</v>
       </c>
-      <c r="R279" t="n">
+      <c r="R281" t="n">
         <v>0.004900850445394598</v>
       </c>
-      <c r="S279" t="inlineStr">
+      <c r="S281" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO279" t="inlineStr">
+      <c r="AO281" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP279" t="inlineStr">
+      <c r="AP281" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR279" t="inlineStr">
+      <c r="AR281" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS279" t="inlineStr"/>
-      <c r="AT279" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU279" t="inlineStr">
+      <c r="AS281" t="inlineStr"/>
+      <c r="AT281" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU281" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV279" t="inlineStr">
+      <c r="AV281" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW279" t="inlineStr">
+      <c r="AW281" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX279" t="inlineStr">
+      <c r="AX281" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY279" t="inlineStr">
+      <c r="AY281" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ279" t="inlineStr">
+      <c r="AZ281" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA279" t="inlineStr">
+      <c r="BA281" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB279" t="inlineStr">
+      <c r="BB281" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC279" t="inlineStr">
+      <c r="BC281" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -49190,7 +49583,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="10">
@@ -49200,7 +49593,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="11">
@@ -49220,7 +49613,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d100/2026-2029.xlsx
+++ b/diseases/d100/2026-2029.xlsx
@@ -44325,13 +44325,13 @@
         </is>
       </c>
       <c r="N252" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O252" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R252" t="n">
-        <v>0.2242771302788003</v>
+        <v>0.214932249850517</v>
       </c>
       <c r="S252" t="inlineStr">
         <is>
@@ -44489,10 +44489,10 @@
         </is>
       </c>
       <c r="N253" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O253" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="U253" t="inlineStr">
         <is>
@@ -48841,13 +48841,13 @@
         </is>
       </c>
       <c r="N278" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O278" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="R278" t="n">
-        <v>0.05306927477386519</v>
+        <v>0.1238283078056854</v>
       </c>
       <c r="S278" t="inlineStr">
         <is>
@@ -49005,10 +49005,10 @@
         </is>
       </c>
       <c r="N279" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O279" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="U279" t="inlineStr">
         <is>
@@ -49645,7 +49645,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2499</v>
+        <v>2502</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d100/2026-2029.xlsx
+++ b/diseases/d100/2026-2029.xlsx
@@ -48293,13 +48293,13 @@
         </is>
       </c>
       <c r="N275" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O275" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R275" t="n">
-        <v>0.03557618341728275</v>
+        <v>0.05336427512592412</v>
       </c>
       <c r="S275" t="inlineStr">
         <is>
@@ -48457,10 +48457,10 @@
         </is>
       </c>
       <c r="N276" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O276" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U276" t="inlineStr">
         <is>
@@ -49645,7 +49645,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2502</v>
+        <v>2503</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d100/2026-2029.xlsx
+++ b/diseases/d100/2026-2029.xlsx
@@ -49467,6 +49467,545 @@
         </is>
       </c>
     </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>haemophilus-influenzae</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>流感嗜血杆菌</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N282" t="n">
+        <v>0</v>
+      </c>
+      <c r="O282" t="n">
+        <v>0</v>
+      </c>
+      <c r="P282" t="n">
+        <v>0</v>
+      </c>
+      <c r="R282" t="n">
+        <v>0</v>
+      </c>
+      <c r="S282" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA282" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO282" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP282" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ282" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS282" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B; SER_SG_HIST_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
+      <c r="AT282" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU282" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV282" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW282" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX282" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY282" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ282" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA282" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB282" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC282" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>haemophilus-influenzae</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>流感嗜血杆菌</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N283" t="n">
+        <v>0</v>
+      </c>
+      <c r="O283" t="n">
+        <v>0</v>
+      </c>
+      <c r="P283" t="n">
+        <v>0</v>
+      </c>
+      <c r="U283" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
+      <c r="V283" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
+      <c r="W283" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X283" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae type b</t>
+        </is>
+      </c>
+      <c r="Y283" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z283" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA283" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB283" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC283" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD283" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE283" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF283" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG283" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH283" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI283" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ283" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK283" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM283" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN283" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO283" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP283" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ283" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS283" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B; SER_SG_HIST_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
+      <c r="AT283" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU283" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV283" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW283" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX283" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY283" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ283" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA283" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB283" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC283" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>haemophilus-influenzae</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>流感嗜血杆菌</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N284" t="n">
+        <v>38</v>
+      </c>
+      <c r="O284" t="n">
+        <v>38</v>
+      </c>
+      <c r="R284" t="n">
+        <v>0.01088714490452366</v>
+      </c>
+      <c r="S284" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO284" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP284" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR284" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS284" t="inlineStr"/>
+      <c r="AT284" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU284" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV284" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW284" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX284" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY284" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ284" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA284" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB284" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC284" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -49500,7 +50039,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -49583,7 +50122,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="10">
@@ -49593,7 +50132,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="11">
@@ -49613,7 +50152,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13">
@@ -49645,7 +50184,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2503</v>
+        <v>2541</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d100/2026-2029.xlsx
+++ b/diseases/d100/2026-2029.xlsx
@@ -43345,12 +43345,12 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -43423,42 +43423,42 @@
       </c>
       <c r="AV247" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW247" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ247" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA247" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB247" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC247" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -43490,12 +43490,12 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -43529,100 +43529,81 @@
         </is>
       </c>
       <c r="N248" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O248" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="R248" t="n">
-        <v>0.1592078243215956</v>
+        <v>0</v>
       </c>
       <c r="S248" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U248" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA248" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO248" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP248" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ248" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR248" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS248" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS248" t="inlineStr"/>
       <c r="AT248" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU248" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV248" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ248" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA248" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB248" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC248" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -43649,7 +43630,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -43698,98 +43679,23 @@
       <c r="O249" t="n">
         <v>9</v>
       </c>
+      <c r="R249" t="n">
+        <v>0.1592078243215956</v>
+      </c>
+      <c r="S249" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U249" t="inlineStr">
         <is>
           <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
-      <c r="V249" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W249" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X249" t="inlineStr">
-        <is>
-          <t>Syst. H. influenzae-sykdom</t>
-        </is>
-      </c>
-      <c r="Y249" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z249" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA249" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB249" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC249" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD249" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE249" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF249" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG249" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH249" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI249" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ249" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK249" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic disease mapping.</t>
-        </is>
-      </c>
-      <c r="AM249" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN249" t="b">
-        <v>1</v>
       </c>
       <c r="AO249" t="inlineStr">
         <is>
@@ -43888,17 +43794,17 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -43932,22 +43838,39 @@
         </is>
       </c>
       <c r="N250" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O250" t="n">
-        <v>0</v>
-      </c>
-      <c r="R250" t="n">
-        <v>0</v>
-      </c>
-      <c r="S250" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>9</v>
       </c>
       <c r="U250" t="inlineStr">
         <is>
-          <t>SER_NZ_HAEMOPHILUS_INFLUENZAE_TYPE_B_MONTHLY</t>
+          <t>SER_NO_FHI_103_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V250" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_103_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W250" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X250" t="inlineStr">
+        <is>
+          <t>Syst. H. influenzae-sykdom</t>
+        </is>
+      </c>
+      <c r="Y250" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z250" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA250" t="inlineStr">
@@ -43955,6 +43878,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB250" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC250" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD250" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE250" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF250" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG250" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH250" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI250" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ250" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK250" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic disease mapping.</t>
+        </is>
+      </c>
+      <c r="AM250" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN250" t="b">
+        <v>1</v>
+      </c>
       <c r="AO250" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -43962,7 +43943,7 @@
       </c>
       <c r="AP250" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ250" t="inlineStr">
@@ -43970,57 +43951,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR250" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS250" t="inlineStr">
         <is>
-          <t>SER_NZ_HAEMOPHILUS_INFLUENZAE_TYPE_B_MONTHLY</t>
+          <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="AT250" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU250" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV250" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ250" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA250" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB250" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC250" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -44047,7 +44033,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -44096,98 +44082,23 @@
       <c r="O251" t="n">
         <v>0</v>
       </c>
+      <c r="R251" t="n">
+        <v>0</v>
+      </c>
+      <c r="S251" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U251" t="inlineStr">
         <is>
           <t>SER_NZ_HAEMOPHILUS_INFLUENZAE_TYPE_B_MONTHLY</t>
         </is>
       </c>
-      <c r="V251" t="inlineStr">
-        <is>
-          <t>SER_NZ_HAEMOPHILUS_INFLUENZAE_TYPE_B_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W251" t="inlineStr">
-        <is>
-          <t>SRC_NZ_PHS</t>
-        </is>
-      </c>
-      <c r="X251" t="inlineStr">
-        <is>
-          <t>Haemophilus influenzae type b</t>
-        </is>
-      </c>
-      <c r="Y251" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z251" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA251" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB251" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC251" t="inlineStr">
-        <is>
-          <t>country:NZ:national</t>
-        </is>
-      </c>
-      <c r="AD251" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE251" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF251" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG251" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH251" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI251" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ251" t="inlineStr">
-        <is>
-          <t>NZ_PHS_current</t>
-        </is>
-      </c>
-      <c r="AK251" t="inlineStr">
-        <is>
-          <t>New Zealand PHF Science monthly Haemophilus influenzae type b notifications; the serotype-qualified source series is narrower than unqualified D100.</t>
-        </is>
-      </c>
-      <c r="AM251" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN251" t="b">
-        <v>1</v>
       </c>
       <c r="AO251" t="inlineStr">
         <is>
@@ -44281,17 +44192,17 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -44325,22 +44236,39 @@
         </is>
       </c>
       <c r="N252" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="O252" t="n">
-        <v>23</v>
-      </c>
-      <c r="R252" t="n">
-        <v>0.214932249850517</v>
-      </c>
-      <c r="S252" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="U252" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HAEMOPHILUS_INVASIVE</t>
+          <t>SER_NZ_HAEMOPHILUS_INFLUENZAE_TYPE_B_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V252" t="inlineStr">
+        <is>
+          <t>SER_NZ_HAEMOPHILUS_INFLUENZAE_TYPE_B_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W252" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X252" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae type b</t>
+        </is>
+      </c>
+      <c r="Y252" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z252" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA252" t="inlineStr">
@@ -44348,6 +44276,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB252" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC252" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD252" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE252" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF252" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG252" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH252" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI252" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ252" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK252" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science monthly Haemophilus influenzae type b notifications; the serotype-qualified source series is narrower than unqualified D100.</t>
+        </is>
+      </c>
+      <c r="AM252" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN252" t="b">
+        <v>1</v>
+      </c>
       <c r="AO252" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -44355,7 +44341,7 @@
       </c>
       <c r="AP252" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ252" t="inlineStr">
@@ -44363,62 +44349,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR252" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS252" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HAEMOPHILUS_INVASIVE</t>
+          <t>SER_NZ_HAEMOPHILUS_INFLUENZAE_TYPE_B_MONTHLY</t>
         </is>
       </c>
       <c r="AT252" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU252" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV252" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW252" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ252" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA252" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB252" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC252" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -44445,7 +44426,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -44494,98 +44475,23 @@
       <c r="O253" t="n">
         <v>23</v>
       </c>
+      <c r="R253" t="n">
+        <v>0.214932249850517</v>
+      </c>
+      <c r="S253" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U253" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_HAEMOPHILUS_INVASIVE</t>
         </is>
       </c>
-      <c r="V253" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_HAEMOPHILUS_INVASIVE</t>
-        </is>
-      </c>
-      <c r="W253" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X253" t="inlineStr">
-        <is>
-          <t>Invasiv infektion med Haemophilus influenzae</t>
-        </is>
-      </c>
-      <c r="Y253" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z253" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA253" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB253" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC253" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD253" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE253" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF253" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG253" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH253" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI253" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ253" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK253" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; Source is invasive disease and is not assumed to be type b only.</t>
-        </is>
-      </c>
-      <c r="AM253" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN253" t="b">
-        <v>1</v>
       </c>
       <c r="AO253" t="inlineStr">
         <is>
@@ -44684,17 +44590,17 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -44728,81 +44634,175 @@
         </is>
       </c>
       <c r="N254" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="O254" t="n">
-        <v>33</v>
-      </c>
-      <c r="R254" t="n">
-        <v>0.009454625838138971</v>
-      </c>
-      <c r="S254" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>23</v>
+      </c>
+      <c r="U254" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HAEMOPHILUS_INVASIVE</t>
+        </is>
+      </c>
+      <c r="V254" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HAEMOPHILUS_INVASIVE</t>
+        </is>
+      </c>
+      <c r="W254" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X254" t="inlineStr">
+        <is>
+          <t>Invasiv infektion med Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="Y254" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z254" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA254" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB254" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC254" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD254" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE254" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF254" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG254" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH254" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI254" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ254" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK254" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; Source is invasive disease and is not assumed to be type b only.</t>
+        </is>
+      </c>
+      <c r="AM254" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN254" t="b">
+        <v>1</v>
       </c>
       <c r="AO254" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP254" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ254" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR254" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS254" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS254" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HAEMOPHILUS_INVASIVE</t>
+        </is>
+      </c>
       <c r="AT254" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU254" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV254" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW254" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ254" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA254" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB254" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC254" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -44834,12 +44834,12 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -44864,7 +44864,7 @@
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M255" t="inlineStr">
@@ -44873,13 +44873,13 @@
         </is>
       </c>
       <c r="N255" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="O255" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="R255" t="n">
-        <v>0.004900850445394598</v>
+        <v>0.009454625838138971</v>
       </c>
       <c r="S255" t="inlineStr">
         <is>
@@ -44912,42 +44912,42 @@
       </c>
       <c r="AV255" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW255" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX255" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY255" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ255" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA255" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB255" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC255" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -44979,12 +44979,12 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -45018,93 +45018,81 @@
         </is>
       </c>
       <c r="N256" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O256" t="n">
-        <v>0</v>
-      </c>
-      <c r="P256" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R256" t="n">
-        <v>0</v>
+        <v>0.004900850445394598</v>
       </c>
       <c r="S256" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA256" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO256" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP256" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ256" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS256" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B; SER_SG_HIST_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR256" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS256" t="inlineStr"/>
       <c r="AT256" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU256" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV256" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW256" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY256" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ256" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA256" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB256" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC256" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -45131,7 +45119,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -45183,98 +45171,18 @@
       <c r="P257" t="n">
         <v>0</v>
       </c>
-      <c r="U257" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
-      <c r="V257" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
-      <c r="W257" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X257" t="inlineStr">
-        <is>
-          <t>Haemophilus influenzae type b</t>
-        </is>
-      </c>
-      <c r="Y257" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z257" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R257" t="n">
+        <v>0</v>
+      </c>
+      <c r="S257" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA257" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB257" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC257" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD257" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE257" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF257" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG257" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH257" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI257" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ257" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK257" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM257" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN257" t="b">
-        <v>1</v>
       </c>
       <c r="AO257" t="inlineStr">
         <is>
@@ -45368,17 +45276,17 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -45403,7 +45311,7 @@
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M258" t="inlineStr">
@@ -45412,81 +45320,173 @@
         </is>
       </c>
       <c r="N258" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="O258" t="n">
-        <v>41</v>
-      </c>
-      <c r="R258" t="n">
-        <v>0.01174665634435448</v>
-      </c>
-      <c r="S258" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="P258" t="n">
+        <v>0</v>
+      </c>
+      <c r="U258" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
+      <c r="V258" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
+      <c r="W258" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X258" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae type b</t>
+        </is>
+      </c>
+      <c r="Y258" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z258" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA258" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB258" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC258" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD258" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE258" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF258" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG258" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH258" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI258" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ258" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK258" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM258" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN258" t="b">
+        <v>1</v>
       </c>
       <c r="AO258" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP258" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR258" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS258" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ258" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS258" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B; SER_SG_HIST_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
       <c r="AT258" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU258" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV258" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW258" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX258" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY258" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ258" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA258" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB258" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC258" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -45518,12 +45518,12 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -45548,7 +45548,7 @@
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M259" t="inlineStr">
@@ -45557,13 +45557,13 @@
         </is>
       </c>
       <c r="N259" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="O259" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="R259" t="n">
-        <v>0.004900850445394598</v>
+        <v>0.01174665634435448</v>
       </c>
       <c r="S259" t="inlineStr">
         <is>
@@ -45596,42 +45596,42 @@
       </c>
       <c r="AV259" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW259" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX259" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY259" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ259" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA259" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB259" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC259" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -45663,12 +45663,12 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -45702,93 +45702,81 @@
         </is>
       </c>
       <c r="N260" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O260" t="n">
-        <v>0</v>
-      </c>
-      <c r="P260" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R260" t="n">
-        <v>0</v>
+        <v>0.004900850445394598</v>
       </c>
       <c r="S260" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA260" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO260" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP260" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ260" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS260" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B; SER_SG_HIST_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR260" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS260" t="inlineStr"/>
       <c r="AT260" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU260" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV260" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW260" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY260" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ260" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA260" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB260" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC260" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -45815,7 +45803,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -45867,98 +45855,18 @@
       <c r="P261" t="n">
         <v>0</v>
       </c>
-      <c r="U261" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
-      <c r="V261" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
-      <c r="W261" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X261" t="inlineStr">
-        <is>
-          <t>Haemophilus influenzae type b</t>
-        </is>
-      </c>
-      <c r="Y261" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z261" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R261" t="n">
+        <v>0</v>
+      </c>
+      <c r="S261" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA261" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB261" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC261" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD261" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE261" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF261" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG261" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH261" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI261" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ261" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK261" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM261" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN261" t="b">
-        <v>1</v>
       </c>
       <c r="AO261" t="inlineStr">
         <is>
@@ -46052,17 +45960,17 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -46087,7 +45995,7 @@
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M262" t="inlineStr">
@@ -46096,81 +46004,173 @@
         </is>
       </c>
       <c r="N262" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="O262" t="n">
-        <v>38</v>
-      </c>
-      <c r="R262" t="n">
-        <v>0.01088714490452366</v>
-      </c>
-      <c r="S262" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="P262" t="n">
+        <v>0</v>
+      </c>
+      <c r="U262" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
+      <c r="V262" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
+      <c r="W262" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X262" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae type b</t>
+        </is>
+      </c>
+      <c r="Y262" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z262" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA262" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB262" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC262" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD262" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE262" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF262" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG262" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH262" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI262" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ262" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK262" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM262" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN262" t="b">
+        <v>1</v>
       </c>
       <c r="AO262" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP262" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR262" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS262" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ262" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS262" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B; SER_SG_HIST_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
       <c r="AT262" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU262" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV262" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW262" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX262" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY262" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ262" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA262" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB262" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC262" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -46202,12 +46202,12 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -46232,7 +46232,7 @@
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M263" t="inlineStr">
@@ -46241,13 +46241,13 @@
         </is>
       </c>
       <c r="N263" t="n">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="O263" t="n">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="R263" t="n">
-        <v>0.01143531770592073</v>
+        <v>0.01088714490452366</v>
       </c>
       <c r="S263" t="inlineStr">
         <is>
@@ -46280,42 +46280,42 @@
       </c>
       <c r="AV263" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW263" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX263" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY263" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ263" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA263" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB263" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC263" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -46347,12 +46347,12 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -46386,93 +46386,81 @@
         </is>
       </c>
       <c r="N264" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O264" t="n">
-        <v>0</v>
-      </c>
-      <c r="P264" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="R264" t="n">
-        <v>0</v>
+        <v>0.01143531770592073</v>
       </c>
       <c r="S264" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA264" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO264" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP264" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ264" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS264" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B; SER_SG_HIST_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR264" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS264" t="inlineStr"/>
       <c r="AT264" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU264" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV264" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW264" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX264" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY264" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ264" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA264" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB264" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC264" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -46499,7 +46487,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
@@ -46551,98 +46539,18 @@
       <c r="P265" t="n">
         <v>0</v>
       </c>
-      <c r="U265" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
-      <c r="V265" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
-      <c r="W265" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X265" t="inlineStr">
-        <is>
-          <t>Haemophilus influenzae type b</t>
-        </is>
-      </c>
-      <c r="Y265" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z265" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R265" t="n">
+        <v>0</v>
+      </c>
+      <c r="S265" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA265" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB265" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC265" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD265" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE265" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF265" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG265" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH265" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI265" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ265" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK265" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM265" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN265" t="b">
-        <v>1</v>
       </c>
       <c r="AO265" t="inlineStr">
         <is>
@@ -46736,17 +46644,17 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -46771,7 +46679,7 @@
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M266" t="inlineStr">
@@ -46780,81 +46688,173 @@
         </is>
       </c>
       <c r="N266" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="O266" t="n">
-        <v>30</v>
-      </c>
-      <c r="R266" t="n">
-        <v>0.008595114398308155</v>
-      </c>
-      <c r="S266" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="P266" t="n">
+        <v>0</v>
+      </c>
+      <c r="U266" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
+      <c r="V266" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
+      <c r="W266" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X266" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae type b</t>
+        </is>
+      </c>
+      <c r="Y266" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z266" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA266" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB266" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC266" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD266" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE266" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF266" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG266" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH266" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI266" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ266" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK266" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM266" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN266" t="b">
+        <v>1</v>
       </c>
       <c r="AO266" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP266" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR266" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS266" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ266" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS266" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B; SER_SG_HIST_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
       <c r="AT266" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU266" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV266" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW266" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX266" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY266" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ266" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA266" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB266" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC266" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -46886,12 +46886,12 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -46916,7 +46916,7 @@
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M267" t="inlineStr">
@@ -46925,13 +46925,13 @@
         </is>
       </c>
       <c r="N267" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="O267" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="R267" t="n">
-        <v>0.00653446726052613</v>
+        <v>0.008595114398308155</v>
       </c>
       <c r="S267" t="inlineStr">
         <is>
@@ -46964,42 +46964,42 @@
       </c>
       <c r="AV267" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW267" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX267" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY267" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ267" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA267" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB267" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC267" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -47031,12 +47031,12 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -47070,93 +47070,81 @@
         </is>
       </c>
       <c r="N268" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O268" t="n">
-        <v>0</v>
-      </c>
-      <c r="P268" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R268" t="n">
-        <v>0</v>
+        <v>0.00653446726052613</v>
       </c>
       <c r="S268" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA268" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO268" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP268" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ268" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS268" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B; SER_SG_HIST_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR268" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS268" t="inlineStr"/>
       <c r="AT268" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU268" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV268" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW268" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX268" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY268" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ268" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA268" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB268" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC268" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -47183,7 +47171,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
@@ -47235,98 +47223,18 @@
       <c r="P269" t="n">
         <v>0</v>
       </c>
-      <c r="U269" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
-      <c r="V269" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
-      <c r="W269" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X269" t="inlineStr">
-        <is>
-          <t>Haemophilus influenzae type b</t>
-        </is>
-      </c>
-      <c r="Y269" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z269" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R269" t="n">
+        <v>0</v>
+      </c>
+      <c r="S269" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA269" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB269" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC269" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD269" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE269" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF269" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG269" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH269" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI269" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ269" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK269" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM269" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN269" t="b">
-        <v>1</v>
       </c>
       <c r="AO269" t="inlineStr">
         <is>
@@ -47420,17 +47328,17 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -47455,7 +47363,7 @@
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M270" t="inlineStr">
@@ -47464,81 +47372,173 @@
         </is>
       </c>
       <c r="N270" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="O270" t="n">
-        <v>36</v>
-      </c>
-      <c r="R270" t="n">
-        <v>0.01031413727796979</v>
-      </c>
-      <c r="S270" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="P270" t="n">
+        <v>0</v>
+      </c>
+      <c r="U270" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
+      <c r="V270" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
+      <c r="W270" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X270" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae type b</t>
+        </is>
+      </c>
+      <c r="Y270" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z270" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA270" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB270" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC270" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD270" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE270" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF270" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG270" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH270" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI270" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ270" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK270" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM270" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN270" t="b">
+        <v>1</v>
       </c>
       <c r="AO270" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP270" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR270" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS270" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ270" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS270" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B; SER_SG_HIST_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
       <c r="AT270" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU270" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV270" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW270" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX270" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY270" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ270" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA270" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB270" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC270" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -47570,12 +47570,12 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -47600,7 +47600,7 @@
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M271" t="inlineStr">
@@ -47609,13 +47609,13 @@
         </is>
       </c>
       <c r="N271" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="O271" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="R271" t="n">
-        <v>0.009801700890789196</v>
+        <v>0.01031413727796979</v>
       </c>
       <c r="S271" t="inlineStr">
         <is>
@@ -47648,42 +47648,42 @@
       </c>
       <c r="AV271" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW271" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX271" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY271" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ271" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA271" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB271" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC271" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -47715,12 +47715,12 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -47754,93 +47754,81 @@
         </is>
       </c>
       <c r="N272" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O272" t="n">
-        <v>0</v>
-      </c>
-      <c r="P272" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R272" t="n">
-        <v>0</v>
+        <v>0.009801700890789196</v>
       </c>
       <c r="S272" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA272" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO272" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP272" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ272" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS272" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B; SER_SG_HIST_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR272" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS272" t="inlineStr"/>
       <c r="AT272" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU272" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV272" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW272" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX272" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY272" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ272" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA272" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB272" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC272" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -47867,7 +47855,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
@@ -47919,98 +47907,18 @@
       <c r="P273" t="n">
         <v>0</v>
       </c>
-      <c r="U273" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
-      <c r="V273" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
-      <c r="W273" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X273" t="inlineStr">
-        <is>
-          <t>Haemophilus influenzae type b</t>
-        </is>
-      </c>
-      <c r="Y273" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z273" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R273" t="n">
+        <v>0</v>
+      </c>
+      <c r="S273" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA273" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB273" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC273" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD273" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE273" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF273" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG273" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH273" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI273" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ273" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK273" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM273" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN273" t="b">
-        <v>1</v>
       </c>
       <c r="AO273" t="inlineStr">
         <is>
@@ -48104,17 +48012,17 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -48139,12 +48047,12 @@
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N274" t="n">
@@ -48153,76 +48061,168 @@
       <c r="O274" t="n">
         <v>0</v>
       </c>
-      <c r="R274" t="n">
-        <v>0</v>
-      </c>
-      <c r="S274" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P274" t="n">
+        <v>0</v>
+      </c>
+      <c r="U274" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
+      <c r="V274" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
+      <c r="W274" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X274" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae type b</t>
+        </is>
+      </c>
+      <c r="Y274" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z274" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA274" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB274" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC274" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD274" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE274" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF274" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG274" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH274" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI274" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ274" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK274" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM274" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN274" t="b">
+        <v>1</v>
       </c>
       <c r="AO274" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP274" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR274" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS274" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ274" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS274" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B; SER_SG_HIST_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
       <c r="AT274" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU274" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV274" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW274" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX274" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY274" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ274" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA274" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB274" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC274" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -48254,12 +48254,12 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -48293,100 +48293,81 @@
         </is>
       </c>
       <c r="N275" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O275" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R275" t="n">
-        <v>0.05336427512592412</v>
+        <v>0</v>
       </c>
       <c r="S275" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U275" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1459</t>
-        </is>
-      </c>
-      <c r="AA275" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO275" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP275" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ275" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR275" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS275" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1459</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS275" t="inlineStr"/>
       <c r="AT275" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU275" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV275" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW275" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX275" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY275" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ275" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA275" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB275" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC275" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -48413,7 +48394,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
@@ -48457,103 +48438,28 @@
         </is>
       </c>
       <c r="N276" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O276" t="n">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="R276" t="n">
+        <v>0.1067285502518482</v>
+      </c>
+      <c r="S276" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U276" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
-      <c r="V276" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1459</t>
-        </is>
-      </c>
-      <c r="W276" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X276" t="inlineStr">
-        <is>
-          <t>Haemophilus influenzae,total</t>
-        </is>
-      </c>
-      <c r="Y276" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z276" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA276" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB276" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC276" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD276" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE276" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF276" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG276" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH276" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI276" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ276" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK276" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Use the THL reported total; serotype child rows remain independent unprojected series.</t>
-        </is>
-      </c>
-      <c r="AM276" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN276" t="b">
-        <v>1</v>
       </c>
       <c r="AO276" t="inlineStr">
         <is>
@@ -48652,17 +48558,17 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -48696,81 +48602,175 @@
         </is>
       </c>
       <c r="N277" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O277" t="n">
-        <v>0</v>
-      </c>
-      <c r="R277" t="n">
-        <v>0</v>
-      </c>
-      <c r="S277" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="U277" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1459</t>
+        </is>
+      </c>
+      <c r="V277" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1459</t>
+        </is>
+      </c>
+      <c r="W277" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X277" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae,total</t>
+        </is>
+      </c>
+      <c r="Y277" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z277" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA277" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB277" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC277" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD277" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE277" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF277" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG277" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH277" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI277" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ277" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK277" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Use the THL reported total; serotype child rows remain independent unprojected series.</t>
+        </is>
+      </c>
+      <c r="AM277" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN277" t="b">
+        <v>1</v>
       </c>
       <c r="AO277" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP277" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ277" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR277" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS277" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS277" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1459</t>
+        </is>
+      </c>
       <c r="AT277" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU277" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV277" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW277" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX277" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY277" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ277" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA277" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB277" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC277" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -48802,12 +48802,12 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -48841,100 +48841,81 @@
         </is>
       </c>
       <c r="N278" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O278" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R278" t="n">
-        <v>0.1238283078056854</v>
+        <v>0</v>
       </c>
       <c r="S278" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U278" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA278" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO278" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP278" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ278" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR278" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS278" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS278" t="inlineStr"/>
       <c r="AT278" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU278" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV278" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW278" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX278" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY278" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ278" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA278" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB278" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC278" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -48961,7 +48942,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
@@ -49010,98 +48991,23 @@
       <c r="O279" t="n">
         <v>7</v>
       </c>
+      <c r="R279" t="n">
+        <v>0.1238283078056854</v>
+      </c>
+      <c r="S279" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U279" t="inlineStr">
         <is>
           <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
-      <c r="V279" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W279" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X279" t="inlineStr">
-        <is>
-          <t>Syst. H. influenzae-sykdom</t>
-        </is>
-      </c>
-      <c r="Y279" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z279" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA279" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB279" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC279" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD279" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE279" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF279" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG279" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH279" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI279" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ279" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK279" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic disease mapping.</t>
-        </is>
-      </c>
-      <c r="AM279" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN279" t="b">
-        <v>1</v>
       </c>
       <c r="AO279" t="inlineStr">
         <is>
@@ -49200,17 +49106,17 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -49235,7 +49141,7 @@
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M280" t="inlineStr">
@@ -49244,81 +49150,175 @@
         </is>
       </c>
       <c r="N280" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="O280" t="n">
-        <v>21</v>
-      </c>
-      <c r="R280" t="n">
-        <v>0.006016580078815709</v>
-      </c>
-      <c r="S280" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>7</v>
+      </c>
+      <c r="U280" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_103_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V280" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_103_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W280" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X280" t="inlineStr">
+        <is>
+          <t>Syst. H. influenzae-sykdom</t>
+        </is>
+      </c>
+      <c r="Y280" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z280" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA280" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB280" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC280" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD280" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE280" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF280" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG280" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH280" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI280" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ280" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK280" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic disease mapping.</t>
+        </is>
+      </c>
+      <c r="AM280" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN280" t="b">
+        <v>1</v>
       </c>
       <c r="AO280" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP280" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ280" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR280" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS280" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS280" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_103_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT280" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU280" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV280" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW280" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX280" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY280" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ280" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA280" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB280" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC280" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -49350,12 +49350,12 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -49380,7 +49380,7 @@
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="M281" t="inlineStr">
@@ -49389,13 +49389,13 @@
         </is>
       </c>
       <c r="N281" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="O281" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="R281" t="n">
-        <v>0.004900850445394598</v>
+        <v>0.006016580078815709</v>
       </c>
       <c r="S281" t="inlineStr">
         <is>
@@ -49428,42 +49428,42 @@
       </c>
       <c r="AV281" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW281" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX281" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY281" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ281" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA281" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB281" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC281" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -49495,12 +49495,12 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -49534,93 +49534,81 @@
         </is>
       </c>
       <c r="N282" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O282" t="n">
-        <v>0</v>
-      </c>
-      <c r="P282" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R282" t="n">
-        <v>0</v>
+        <v>0.004900850445394598</v>
       </c>
       <c r="S282" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA282" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO282" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP282" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ282" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS282" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B; SER_SG_HIST_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR282" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS282" t="inlineStr"/>
       <c r="AT282" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU282" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV282" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW282" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX282" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY282" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ282" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA282" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB282" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC282" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -49647,7 +49635,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
@@ -49699,98 +49687,18 @@
       <c r="P283" t="n">
         <v>0</v>
       </c>
-      <c r="U283" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
-      <c r="V283" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
-      <c r="W283" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X283" t="inlineStr">
-        <is>
-          <t>Haemophilus influenzae type b</t>
-        </is>
-      </c>
-      <c r="Y283" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z283" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R283" t="n">
+        <v>0</v>
+      </c>
+      <c r="S283" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA283" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB283" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC283" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD283" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE283" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF283" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG283" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH283" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI283" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ283" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK283" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM283" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN283" t="b">
-        <v>1</v>
       </c>
       <c r="AO283" t="inlineStr">
         <is>
@@ -49884,123 +49792,1044 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>流感嗜血杆菌</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N284" t="n">
+        <v>0</v>
+      </c>
+      <c r="O284" t="n">
+        <v>0</v>
+      </c>
+      <c r="P284" t="n">
+        <v>0</v>
+      </c>
+      <c r="U284" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
+      <c r="V284" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
+      <c r="W284" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X284" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae type b</t>
+        </is>
+      </c>
+      <c r="Y284" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z284" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA284" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB284" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC284" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD284" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE284" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF284" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG284" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH284" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI284" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ284" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK284" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM284" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN284" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO284" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP284" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ284" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS284" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B; SER_SG_HIST_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
+      <c r="AT284" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU284" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV284" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW284" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX284" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY284" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ284" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA284" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB284" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC284" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>haemophilus-influenzae</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
           <t>public_projection</t>
         </is>
       </c>
-      <c r="F284" t="inlineStr">
+      <c r="F285" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G284" t="inlineStr">
+      <c r="G285" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="H284" t="inlineStr">
-        <is>
-          <t>D100</t>
-        </is>
-      </c>
-      <c r="I284" t="inlineStr">
-        <is>
-          <t>Haemophilus influenzae</t>
-        </is>
-      </c>
-      <c r="J284" t="inlineStr">
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
         <is>
           <t>流感嗜血杆菌</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr">
+      <c r="K285" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L284" t="inlineStr">
+      <c r="L285" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="M284" t="inlineStr">
+      <c r="M285" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N284" t="n">
+      <c r="N285" t="n">
         <v>38</v>
       </c>
-      <c r="O284" t="n">
+      <c r="O285" t="n">
         <v>38</v>
       </c>
-      <c r="R284" t="n">
+      <c r="R285" t="n">
         <v>0.01088714490452366</v>
       </c>
-      <c r="S284" t="inlineStr">
+      <c r="S285" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO284" t="inlineStr">
+      <c r="AO285" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP284" t="inlineStr">
+      <c r="AP285" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR284" t="inlineStr">
+      <c r="AR285" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS284" t="inlineStr"/>
-      <c r="AT284" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU284" t="inlineStr">
+      <c r="AS285" t="inlineStr"/>
+      <c r="AT285" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU285" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV284" t="inlineStr">
+      <c r="AV285" t="inlineStr">
         <is>
           <t>nndss_api</t>
         </is>
       </c>
-      <c r="AW284" t="inlineStr">
+      <c r="AW285" t="inlineStr">
         <is>
           <t>US CDC NNDSS</t>
         </is>
       </c>
-      <c r="AX284" t="inlineStr">
+      <c r="AX285" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
-      <c r="AY284" t="inlineStr">
+      <c r="AY285" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="AZ284" t="inlineStr">
+      <c r="AZ285" t="inlineStr">
         <is>
           <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
-      <c r="BA284" t="inlineStr">
+      <c r="BA285" t="inlineStr">
         <is>
           <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
-      <c r="BB284" t="inlineStr">
+      <c r="BB285" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
-      <c r="BC284" t="inlineStr">
+      <c r="BC285" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>haemophilus-influenzae</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>流感嗜血杆菌</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N286" t="n">
+        <v>6</v>
+      </c>
+      <c r="O286" t="n">
+        <v>6</v>
+      </c>
+      <c r="R286" t="n">
+        <v>0.004900850445394598</v>
+      </c>
+      <c r="S286" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO286" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP286" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR286" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS286" t="inlineStr"/>
+      <c r="AT286" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU286" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV286" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW286" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX286" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY286" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ286" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA286" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB286" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC286" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>haemophilus-influenzae</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>流感嗜血杆菌</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N287" t="n">
+        <v>0</v>
+      </c>
+      <c r="O287" t="n">
+        <v>0</v>
+      </c>
+      <c r="P287" t="n">
+        <v>0</v>
+      </c>
+      <c r="R287" t="n">
+        <v>0</v>
+      </c>
+      <c r="S287" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA287" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO287" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP287" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ287" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS287" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B; SER_SG_HIST_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
+      <c r="AT287" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU287" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV287" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW287" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX287" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY287" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ287" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA287" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB287" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC287" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>haemophilus-influenzae</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>流感嗜血杆菌</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N288" t="n">
+        <v>0</v>
+      </c>
+      <c r="O288" t="n">
+        <v>0</v>
+      </c>
+      <c r="P288" t="n">
+        <v>0</v>
+      </c>
+      <c r="U288" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
+      <c r="V288" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
+      <c r="W288" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X288" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae type b</t>
+        </is>
+      </c>
+      <c r="Y288" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z288" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA288" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB288" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC288" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD288" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE288" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF288" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG288" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH288" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI288" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ288" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK288" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM288" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN288" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO288" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP288" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ288" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS288" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B; SER_SG_HIST_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
+      <c r="AT288" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU288" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV288" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW288" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX288" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY288" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ288" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA288" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB288" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC288" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>haemophilus-influenzae</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>流感嗜血杆菌</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N289" t="n">
+        <v>28</v>
+      </c>
+      <c r="O289" t="n">
+        <v>28</v>
+      </c>
+      <c r="R289" t="n">
+        <v>0.00802210677175428</v>
+      </c>
+      <c r="S289" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO289" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP289" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR289" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS289" t="inlineStr"/>
+      <c r="AT289" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU289" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV289" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW289" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX289" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY289" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ289" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA289" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB289" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC289" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -50039,7 +50868,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -50122,7 +50951,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>206</v>
+        <v>210</v>
       </c>
     </row>
     <row r="10">
@@ -50132,7 +50961,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>283</v>
+        <v>288</v>
       </c>
     </row>
     <row r="11">
@@ -50152,7 +50981,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13">
@@ -50184,7 +51013,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2541</v>
+        <v>2578</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d100/2026-2029.xlsx
+++ b/diseases/d100/2026-2029.xlsx
@@ -48293,13 +48293,13 @@
         </is>
       </c>
       <c r="N275" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O275" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R275" t="n">
-        <v>0</v>
+        <v>0.01469124727807916</v>
       </c>
       <c r="S275" t="inlineStr">
         <is>
@@ -48438,13 +48438,13 @@
         </is>
       </c>
       <c r="N276" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O276" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R276" t="n">
-        <v>0.1067285502518482</v>
+        <v>0.1778809170864138</v>
       </c>
       <c r="S276" t="inlineStr">
         <is>
@@ -48602,10 +48602,10 @@
         </is>
       </c>
       <c r="N277" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O277" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U277" t="inlineStr">
         <is>
@@ -50832,6 +50832,1238 @@
       <c r="BC289" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>haemophilus-influenzae</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>流感嗜血杆菌</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N290" t="n">
+        <v>6</v>
+      </c>
+      <c r="O290" t="n">
+        <v>6</v>
+      </c>
+      <c r="R290" t="n">
+        <v>0.004900850445394598</v>
+      </c>
+      <c r="S290" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO290" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP290" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR290" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS290" t="inlineStr"/>
+      <c r="AT290" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU290" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV290" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW290" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX290" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY290" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ290" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA290" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB290" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC290" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>haemophilus-influenzae</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>流感嗜血杆菌</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N291" t="n">
+        <v>0</v>
+      </c>
+      <c r="O291" t="n">
+        <v>0</v>
+      </c>
+      <c r="P291" t="n">
+        <v>0</v>
+      </c>
+      <c r="R291" t="n">
+        <v>0</v>
+      </c>
+      <c r="S291" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA291" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO291" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP291" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ291" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS291" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B; SER_SG_HIST_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
+      <c r="AT291" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU291" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV291" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW291" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX291" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY291" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ291" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA291" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB291" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC291" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>haemophilus-influenzae</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>流感嗜血杆菌</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M292" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N292" t="n">
+        <v>0</v>
+      </c>
+      <c r="O292" t="n">
+        <v>0</v>
+      </c>
+      <c r="P292" t="n">
+        <v>0</v>
+      </c>
+      <c r="U292" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
+      <c r="V292" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
+      <c r="W292" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X292" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae type b</t>
+        </is>
+      </c>
+      <c r="Y292" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z292" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA292" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB292" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC292" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD292" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE292" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF292" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG292" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH292" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI292" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ292" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK292" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM292" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN292" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO292" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP292" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ292" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS292" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B; SER_SG_HIST_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
+      <c r="AT292" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU292" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV292" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW292" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX292" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY292" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ292" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA292" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB292" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC292" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>haemophilus-influenzae</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>流感嗜血杆菌</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="M293" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N293" t="n">
+        <v>36</v>
+      </c>
+      <c r="O293" t="n">
+        <v>36</v>
+      </c>
+      <c r="R293" t="n">
+        <v>0.01031413727796979</v>
+      </c>
+      <c r="S293" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO293" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP293" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR293" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS293" t="inlineStr"/>
+      <c r="AT293" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU293" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV293" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW293" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX293" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY293" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ293" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA293" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB293" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC293" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>haemophilus-influenzae</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>流感嗜血杆菌</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M294" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N294" t="n">
+        <v>0</v>
+      </c>
+      <c r="O294" t="n">
+        <v>0</v>
+      </c>
+      <c r="R294" t="n">
+        <v>0</v>
+      </c>
+      <c r="S294" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U294" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1459</t>
+        </is>
+      </c>
+      <c r="AA294" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO294" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP294" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ294" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR294" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS294" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1459</t>
+        </is>
+      </c>
+      <c r="AT294" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU294" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV294" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW294" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX294" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY294" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ294" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA294" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB294" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC294" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>haemophilus-influenzae</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>流感嗜血杆菌</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N295" t="n">
+        <v>0</v>
+      </c>
+      <c r="O295" t="n">
+        <v>0</v>
+      </c>
+      <c r="U295" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1459</t>
+        </is>
+      </c>
+      <c r="V295" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1459</t>
+        </is>
+      </c>
+      <c r="W295" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X295" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae,total</t>
+        </is>
+      </c>
+      <c r="Y295" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z295" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA295" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB295" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC295" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD295" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE295" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF295" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG295" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH295" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI295" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ295" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK295" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Use the THL reported total; serotype child rows remain independent unprojected series.</t>
+        </is>
+      </c>
+      <c r="AM295" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN295" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO295" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP295" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ295" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR295" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS295" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1459</t>
+        </is>
+      </c>
+      <c r="AT295" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU295" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV295" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW295" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX295" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY295" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ295" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA295" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB295" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC295" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>haemophilus-influenzae</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>流感嗜血杆菌</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M296" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N296" t="n">
+        <v>0</v>
+      </c>
+      <c r="O296" t="n">
+        <v>0</v>
+      </c>
+      <c r="R296" t="n">
+        <v>0</v>
+      </c>
+      <c r="S296" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO296" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP296" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR296" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS296" t="inlineStr"/>
+      <c r="AT296" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU296" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV296" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW296" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX296" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY296" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ296" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA296" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB296" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC296" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -50868,7 +52100,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -50951,7 +52183,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>210</v>
+        <v>215</v>
       </c>
     </row>
     <row r="10">
@@ -50961,7 +52193,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>288</v>
+        <v>295</v>
       </c>
     </row>
     <row r="11">
@@ -50981,7 +52213,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13">
@@ -51013,7 +52245,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2578</v>
+        <v>2628</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d100/2026-2029.xlsx
+++ b/diseases/d100/2026-2029.xlsx
@@ -2392,7 +2392,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -7878,7 +7878,7 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN42" t="b">
@@ -13216,7 +13216,7 @@
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN72" t="b">
@@ -18945,7 +18945,7 @@
       </c>
       <c r="AM104" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN104" t="b">
@@ -24277,7 +24277,7 @@
       </c>
       <c r="AM134" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN134" t="b">
@@ -31432,7 +31432,7 @@
       </c>
       <c r="AM176" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN176" t="b">
@@ -37876,7 +37876,7 @@
       </c>
       <c r="AM214" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN214" t="b">
@@ -43930,7 +43930,7 @@
       </c>
       <c r="AM250" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN250" t="b">
@@ -48986,13 +48986,13 @@
         </is>
       </c>
       <c r="N279" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="O279" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="R279" t="n">
-        <v>0.1238283078056854</v>
+        <v>0.1945873408375057</v>
       </c>
       <c r="S279" t="inlineStr">
         <is>
@@ -49150,10 +49150,10 @@
         </is>
       </c>
       <c r="N280" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="O280" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="U280" t="inlineStr">
         <is>
@@ -49242,7 +49242,7 @@
       </c>
       <c r="AM280" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN280" t="b">
@@ -52245,7 +52245,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2628</v>
+        <v>2632</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d100/2026-2029.xlsx
+++ b/diseases/d100/2026-2029.xlsx
@@ -60690,13 +60690,13 @@
         </is>
       </c>
       <c r="N350" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O350" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R350" t="n">
-        <v>0</v>
+        <v>0.03557618341728275</v>
       </c>
       <c r="S350" t="inlineStr">
         <is>
@@ -60854,10 +60854,10 @@
         </is>
       </c>
       <c r="N351" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O351" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U351" t="inlineStr">
         <is>
@@ -61243,13 +61243,13 @@
         </is>
       </c>
       <c r="N353" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O353" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R353" t="n">
-        <v>0</v>
+        <v>0.08844879128977531</v>
       </c>
       <c r="S353" t="inlineStr">
         <is>
@@ -61407,10 +61407,10 @@
         </is>
       </c>
       <c r="N354" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O354" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U354" t="inlineStr">
         <is>
@@ -61726,6 +61726,151 @@
       <c r="BC355" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>haemophilus-influenzae</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>流感嗜血杆菌</t>
+        </is>
+      </c>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M356" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N356" t="n">
+        <v>10</v>
+      </c>
+      <c r="O356" t="n">
+        <v>10</v>
+      </c>
+      <c r="R356" t="n">
+        <v>0.008168084075657663</v>
+      </c>
+      <c r="S356" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO356" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP356" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR356" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS356" t="inlineStr"/>
+      <c r="AT356" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU356" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV356" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW356" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX356" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY356" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ356" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA356" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB356" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC356" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -61762,7 +61907,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -61845,7 +61990,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10">
@@ -61855,7 +62000,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="11">
@@ -61907,7 +62052,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2726</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d100/2026-2029.xlsx
+++ b/diseases/d100/2026-2029.xlsx
@@ -4549,9 +4549,6 @@
       <c r="O24" t="n">
         <v>4</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0.001146015253107754</v>
       </c>
@@ -5244,9 +5241,6 @@
       <c r="O28" t="n">
         <v>71</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0.02034177074266263</v>
       </c>
@@ -5939,9 +5933,6 @@
       <c r="O32" t="n">
         <v>53</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0.01518470210367774</v>
       </c>
@@ -6634,9 +6625,6 @@
       <c r="O36" t="n">
         <v>65</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0.018622747863001</v>
       </c>
@@ -7329,9 +7317,6 @@
       <c r="O40" t="n">
         <v>55</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0.01575770973023162</v>
       </c>
@@ -11808,9 +11793,6 @@
       <c r="O66" t="n">
         <v>49</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0.01403868685056999</v>
       </c>
@@ -12503,9 +12485,6 @@
       <c r="O70" t="n">
         <v>43</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0.01231966397090836</v>
       </c>
@@ -13198,9 +13177,6 @@
       <c r="O74" t="n">
         <v>47</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0.01346567922401611</v>
       </c>
@@ -13893,9 +13869,6 @@
       <c r="O78" t="n">
         <v>53</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0.01518470210367774</v>
       </c>
@@ -17413,13 +17386,13 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="O99" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="R99" t="n">
-        <v>0.2523117715636503</v>
+        <v>0.2336220107070837</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -17577,10 +17550,10 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="O100" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="U100" t="inlineStr">
         <is>
@@ -18363,9 +18336,6 @@
       <c r="O104" t="n">
         <v>45</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0.01289267159746223</v>
       </c>
@@ -19058,9 +19028,6 @@
       <c r="O108" t="n">
         <v>51</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0.01461169447712387</v>
       </c>
@@ -19753,9 +19720,6 @@
       <c r="O112" t="n">
         <v>51</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0.01461169447712387</v>
       </c>
@@ -20448,9 +20412,6 @@
       <c r="O116" t="n">
         <v>53</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0.01518470210367774</v>
       </c>
@@ -24356,13 +24317,13 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O139" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="R139" t="n">
-        <v>0.1308283259959668</v>
+        <v>0.1121385651394002</v>
       </c>
       <c r="S139" t="inlineStr">
         <is>
@@ -24520,10 +24481,10 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O140" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="U140" t="inlineStr">
         <is>
@@ -24912,9 +24873,6 @@
       <c r="O142" t="n">
         <v>43</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>0.01231966397090836</v>
       </c>
@@ -25607,9 +25565,6 @@
       <c r="O146" t="n">
         <v>54</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0.01547120591695468</v>
       </c>
@@ -26302,9 +26257,6 @@
       <c r="O150" t="n">
         <v>54</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0.01547120591695468</v>
       </c>
@@ -26997,9 +26949,6 @@
       <c r="O154" t="n">
         <v>43</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>0.01231966397090836</v>
       </c>
@@ -31470,9 +31419,6 @@
       <c r="O180" t="n">
         <v>45</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>0.01289267159746223</v>
       </c>
@@ -32160,16 +32106,13 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O184" t="n">
-        <v>39</v>
-      </c>
-      <c r="Q184" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="R184" t="n">
-        <v>0.0111736487178006</v>
+        <v>0.01088714490452366</v>
       </c>
       <c r="S184" t="inlineStr">
         <is>
@@ -32860,9 +32803,6 @@
       <c r="O188" t="n">
         <v>57</v>
       </c>
-      <c r="Q188" t="n">
-        <v>0</v>
-      </c>
       <c r="R188" t="n">
         <v>0.0163307173567855</v>
       </c>
@@ -33555,9 +33495,6 @@
       <c r="O192" t="n">
         <v>6</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
       <c r="R192" t="n">
         <v>0.001719022879661631</v>
       </c>
@@ -61871,6 +61808,156 @@
       <c r="BC356" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>haemophilus-influenzae</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>流感嗜血杆菌</t>
+        </is>
+      </c>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M357" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N357" t="n">
+        <v>39</v>
+      </c>
+      <c r="O357" t="n">
+        <v>39</v>
+      </c>
+      <c r="R357" t="n">
+        <v>0.0111736487178006</v>
+      </c>
+      <c r="S357" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA357" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO357" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP357" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR357" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS357" t="inlineStr"/>
+      <c r="AT357" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU357" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV357" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW357" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX357" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY357" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ357" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA357" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB357" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC357" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -61907,7 +61994,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -61990,7 +62077,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10">
@@ -62000,7 +62087,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="11">
@@ -62052,7 +62139,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2743</v>
+        <v>2777</v>
       </c>
     </row>
     <row r="16">
